--- a/Article_data/Step 3 - PRODCOM results.xlsx
+++ b/Article_data/Step 3 - PRODCOM results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\nicolas\projects\202604-paper-1-supplementary-code\Article_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{168116C2-FC68-4220-B783-2E5852996536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A1107EF-031A-4030-A1C2-AD29DCE61D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4788" yWindow="-17388" windowWidth="30936" windowHeight="16776" tabRatio="570" xr2:uid="{EE4678C9-3BCB-4D41-A2DA-6855614353C7}"/>
+    <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" tabRatio="570" xr2:uid="{EE4678C9-3BCB-4D41-A2DA-6855614353C7}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="4" r:id="rId1"/>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7908" uniqueCount="3138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7909" uniqueCount="3139">
   <si>
     <t>freq</t>
   </si>
@@ -8303,9 +8303,6 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This file is used to perform screening on the top most produced and imported products obtained from Prodcom data processing using the related Python notebook. LCI datasets are associated to the selected hotspots. The final output is a CSV file that can be processed by the environmental hotspot calculation Python notebook.</t>
-  </si>
-  <si>
     <t>Note</t>
   </si>
   <si>
@@ -9311,15 +9308,6 @@
     <t>Note:</t>
   </si>
   <si>
-    <t>Prodcom data obtained from "Extract Prodcom data.ipynb"</t>
-  </si>
-  <si>
-    <t>The "In scope" column is filtered to only show rows with no identified issues. The identification process was performed iteratively and manually over the top products in terms of availability (i.e., local production + imports in the EU27). Therefore, only the top 50 products (after filtering) should be considered analyzed by the authors.</t>
-  </si>
-  <si>
-    <t>Data and necessary calculation to split polyamides and isocyanates. Prodcom products into separate product matching with Ecoinvent datasets</t>
-  </si>
-  <si>
     <t>290511</t>
   </si>
   <si>
@@ -9329,9 +9317,6 @@
     <t>Ecoinvent 3.12 activity region 5 share</t>
   </si>
   <si>
-    <t>When determining the Ecoinvent regions, if local availability of a product in Europe was 80% or more, we assumed 100% RER or RER w/o RU. See "Get product importers from BACI.ipynb" file in the SI for details on the calculation of import shares from the different regions and countries. The table should be exported as CSV and imported into the "Calculate product footprints and generate hotspot figure.ipynb" notebook.</t>
-  </si>
-  <si>
     <t>Ecoinvent activity name or proxy</t>
   </si>
   <si>
@@ -9344,9 +9329,6 @@
     <t>Hotspot products export</t>
   </si>
   <si>
-    <t>The table below is an extraction of the table from the previous sheet, taking the top products in the list after screening and ecoinvent matching. Also polyamides and isocyanates were disaggregated below. Table to be exported for use as input CSV in the footprint calculation notebook.</t>
-  </si>
-  <si>
     <t>Tested with Ecoinvent 3.11 and 3.12.</t>
   </si>
   <si>
@@ -9446,12 +9428,6 @@
     <t>Pearson correlation EU27 2019 vs 2022</t>
   </si>
   <si>
-    <t>Calculate R² correlation coefficient for sensitivity analysis.</t>
-  </si>
-  <si>
-    <t>Refer to SM document for more details</t>
-  </si>
-  <si>
     <t>Add sensitivity analysis</t>
   </si>
   <si>
@@ -9467,9 +9443,6 @@
     <t>Split Polyamides &amp; Isocyanates</t>
   </si>
   <si>
-    <t>Calculates the correlation coefficient of the PRODCOM products' mass to total mass</t>
-  </si>
-  <si>
     <t>Rename Calculations sheet and add End-of-life fates sheet</t>
   </si>
   <si>
@@ -9500,9 +9473,6 @@
     <t>Incinerated</t>
   </si>
   <si>
-    <t>Calculate end-of-life plastic waste fate shares</t>
-  </si>
-  <si>
     <t>Total</t>
   </si>
   <si>
@@ -9573,6 +9543,45 @@
   </si>
   <si>
     <t>Cleanings</t>
+  </si>
+  <si>
+    <t>R² correlation coefficient comparing the relative share of the available quantities of each PRODCOM product (20.14 and 20.16 categories), comparing 2019 and 2022. Refer to SM document for more details</t>
+  </si>
+  <si>
+    <t>Available quantity correlation between 2019 and 2022 series, for sensitivity analysis.</t>
+  </si>
+  <si>
+    <t>The table below is an extraction of the table from the previous sheet, taking the top products in the list after screening and ecoinvent matching. Also polyamides and isocyanates were disaggregated below. Table to be exported for use as input CSV in the footprint calculation notebook.
+When determining the Ecoinvent regions, if local availability of a product in Europe was 80% or more, we assumed 100% RER or RER w/o RU. See "Get product importers from BACI.ipynb" file in the SI for details on the calculation of import shares from the different regions and countries. The table should be exported as CSV and imported into the "Calculate product footprints and generate hotspot figure.ipynb" notebook.</t>
+  </si>
+  <si>
+    <t>Extraction of the top PRODCOM products (available quantity), with disaggregation of polyamides and isocyanates. Additional data for footprint calculation. For export to CSV.</t>
+  </si>
+  <si>
+    <t>End-of-life fate shares of plastic waste.</t>
+  </si>
+  <si>
+    <t>Data and necessary calculation to split polyamides and isocyanates PRODCOM products into separate products for matching with Ecoinvent datasets.</t>
+  </si>
+  <si>
+    <t>Correlation coefficient of the PRODCOM products' mass to total mass.</t>
+  </si>
+  <si>
+    <t>PRODCOM data obtained from "Python_notebooks/Extract PRODCOM data.ipynb". The "In scope" column is filtered to only show rows with no identified issues. The identification process was performed iteratively and manually over the top products in terms of availability (i.e., local production + imports in the EU27). Therefore, only the top 50 products (after filtering) should be considered analyzed by the authors.</t>
+  </si>
+  <si>
+    <t>PRODCOM data: local production, import, export. Regions: France (FR) and the EU (EU27_2020). Years: 2019 and 2022. Further filtering of out of scope products.</t>
+  </si>
+  <si>
+    <t>This file is used to perform screening on the top most produced and imported products obtained from PRODCOM data processing using the related Python notebook: "Python_notebooks/Extract PRODCOM data.ipynb". LCI datasets are associated to the selected hotspots. The final output is a CSV file that can be processed by the environmental hotspot calculation Python notebook: "Python_notebooks/Calculate hotspot products footprints and contributions.ipynb".
+Local production, imports and exports quantities in physical unit (i.e., kilogram mostly) of basic organic chemicals and plastics in France and in the EU27 for the years 2019 and 2022. Filtering of the top products to remove inorganics.
+Disaggregating of some products into their major components: polyamides (PA-6 and PA-6,6) and isocyanates (MDI and TDI).
+Match top products (N=57, including disaggregated products) to representative Ecoinvent activity, HS22 code and carbon content.
+Estimated Ecoinvent geography representativity of the top products for the EU27.
+Estimated generic end-of-life fate shares of the top products.</t>
+  </si>
+  <si>
+    <t>Update descriptions</t>
   </si>
 </sst>
 </file>
@@ -9965,7 +9974,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="8" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="3" applyBorder="1"/>
@@ -10162,9 +10171,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="15" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -10176,6 +10182,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="9" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="16">
     <cellStyle name="Accent1" xfId="12" builtinId="29"/>
@@ -10744,7 +10754,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0928EDD3-90ED-405A-8C35-7F6C77CACFAF}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B2:G52"/>
+  <dimension ref="B2:G53"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="35.77734375" customWidth="1"/>
@@ -10805,50 +10815,50 @@
         <v>2712</v>
       </c>
     </row>
-    <row r="12" spans="2:3" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:3" ht="216" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>2713</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>2714</v>
+        <v>3137</v>
       </c>
     </row>
     <row r="13" spans="2:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
+        <v>2714</v>
+      </c>
+      <c r="C13" s="14" t="s">
         <v>2715</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>2716</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
+        <v>2716</v>
+      </c>
+      <c r="C14" s="15" t="s">
         <v>2717</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>2718</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
+        <v>2718</v>
+      </c>
+      <c r="C15" s="15" t="s">
         <v>2719</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>2720</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B18" s="12" t="s">
-        <v>2721</v>
+        <v>2720</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="20" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B20" s="16" t="s">
-        <v>2722</v>
+        <v>2721</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>2715</v>
+        <v>2714</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.3">
@@ -10856,7 +10866,7 @@
         <v>46146</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>2723</v>
+        <v>2722</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.3">
@@ -10864,7 +10874,7 @@
         <v>46242</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>2795</v>
+        <v>2794</v>
       </c>
     </row>
     <row r="23" spans="2:3" s="43" customFormat="1" x14ac:dyDescent="0.3">
@@ -10872,7 +10882,7 @@
         <v>46245</v>
       </c>
       <c r="C23" s="28" t="s">
-        <v>3046</v>
+        <v>3045</v>
       </c>
     </row>
     <row r="24" spans="2:3" s="43" customFormat="1" x14ac:dyDescent="0.3">
@@ -10880,7 +10890,7 @@
         <v>46247</v>
       </c>
       <c r="C24" s="28" t="s">
-        <v>3059</v>
+        <v>3054</v>
       </c>
     </row>
     <row r="25" spans="2:3" s="43" customFormat="1" x14ac:dyDescent="0.3">
@@ -10888,7 +10898,7 @@
         <v>46248</v>
       </c>
       <c r="C25" s="28" t="s">
-        <v>3068</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="26" spans="2:3" s="43" customFormat="1" x14ac:dyDescent="0.3">
@@ -10896,7 +10906,7 @@
         <v>46251</v>
       </c>
       <c r="C26" s="28" t="s">
-        <v>3097</v>
+        <v>3089</v>
       </c>
     </row>
     <row r="27" spans="2:3" s="43" customFormat="1" x14ac:dyDescent="0.3">
@@ -10904,247 +10914,255 @@
         <v>46253</v>
       </c>
       <c r="C27" s="28" t="s">
-        <v>3103</v>
-      </c>
-    </row>
-    <row r="28" spans="2:3" s="43" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="18">
+        <v>3094</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" s="43" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="30">
         <v>46255</v>
       </c>
-      <c r="C28" s="19" t="s">
-        <v>3137</v>
-      </c>
-    </row>
-    <row r="31" spans="2:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B31" s="12" t="s">
+      <c r="C28" s="28" t="s">
+        <v>3127</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" s="43" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B29" s="18">
+        <v>46257</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>3138</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B32" s="12" t="s">
+        <v>2723</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B34" s="16" t="s">
         <v>2724</v>
       </c>
-    </row>
-    <row r="32" spans="2:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B33" s="16" t="s">
+      <c r="C34" s="17" t="s">
+        <v>2713</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B35" s="20" t="s">
         <v>2725</v>
       </c>
-      <c r="C33" s="17" t="s">
-        <v>2713</v>
-      </c>
-    </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B34" s="20" t="s">
+      <c r="C35" s="21" t="s">
         <v>2726</v>
-      </c>
-      <c r="C34" s="21" t="s">
-        <v>2727</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B35" s="73" t="s">
-        <v>3098</v>
-      </c>
-      <c r="C35" s="74" t="str">
-        <f>'Filtered PRODCOM data'!$B$1</f>
-        <v>Prodcom data obtained from "Extract Prodcom data.ipynb"</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B36" s="73" t="s">
-        <v>3099</v>
+        <v>3090</v>
       </c>
       <c r="C36" s="74" t="str">
-        <f>'Correlation EU27 2019-2022'!$B$1</f>
-        <v>Calculates the correlation coefficient of the PRODCOM products' mass to total mass</v>
+        <f>'Filtered PRODCOM data'!$B$1</f>
+        <v>PRODCOM data: local production, import, export. Regions: France (FR) and the EU (EU27_2020). Years: 2019 and 2022. Further filtering of out of scope products.</v>
       </c>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B37" s="73" t="s">
-        <v>3101</v>
+        <v>3091</v>
       </c>
       <c r="C37" s="74" t="str">
-        <f>'Split Polyamides &amp; Isocyanates'!$B$1</f>
-        <v>Data and necessary calculation to split polyamides and isocyanates. Prodcom products into separate product matching with Ecoinvent datasets</v>
+        <f>'Correlation EU27 2019-2022'!$B$1</f>
+        <v>Correlation coefficient of the PRODCOM products' mass to total mass.</v>
       </c>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B38" s="73" t="s">
-        <v>3136</v>
+        <v>3093</v>
       </c>
       <c r="C38" s="74" t="str">
+        <f>'Split Polyamides &amp; Isocyanates'!$B$1</f>
+        <v>Data and necessary calculation to split polyamides and isocyanates PRODCOM products into separate products for matching with Ecoinvent datasets.</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B39" s="73" t="s">
+        <v>3126</v>
+      </c>
+      <c r="C39" s="74" t="str">
         <f>'End-of-life fates'!$B$1</f>
-        <v>Calculate end-of-life plastic waste fate shares</v>
-      </c>
-    </row>
-    <row r="39" spans="2:7" s="43" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="73" t="s">
-        <v>3060</v>
-      </c>
-      <c r="C39" s="74" t="str">
-        <f>'Hotspot products export'!$B$1</f>
-        <v>The table below is an extraction of the table from the previous sheet, taking the top products in the list after screening and ecoinvent matching. Also polyamides and isocyanates were disaggregated below. Table to be exported for use as input CSV in the footprint calculation notebook.</v>
+        <v>End-of-life fate shares of plastic waste.</v>
       </c>
     </row>
     <row r="40" spans="2:7" s="43" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B40" s="73" t="s">
-        <v>3100</v>
+        <v>3055</v>
       </c>
       <c r="C40" s="74" t="str">
+        <f>'Hotspot products export'!$B$1</f>
+        <v>Extraction of the top PRODCOM products (available quantity), with disaggregation of polyamides and isocyanates. Additional data for footprint calculation. For export to CSV.</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" s="43" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="73" t="s">
+        <v>3092</v>
+      </c>
+      <c r="C41" s="74" t="str">
         <f>'Sensitivity analysis'!$B$1</f>
-        <v>Calculate R² correlation coefficient for sensitivity analysis.</v>
-      </c>
-    </row>
-    <row r="41" spans="2:7" s="43" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="75" t="s">
-        <v>2728</v>
-      </c>
-      <c r="C41" s="76" t="str">
+        <v>Available quantity correlation between 2019 and 2022 series, for sensitivity analysis.</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" s="43" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B42" s="75" t="s">
+        <v>2727</v>
+      </c>
+      <c r="C42" s="76" t="str">
         <f>References!$B$1</f>
         <v>Bibliography: list of references used thoughout the workbook</v>
       </c>
     </row>
-    <row r="43" spans="2:7" s="43" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="44" spans="2:7" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="12" t="s">
+    <row r="44" spans="2:7" s="43" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="45" spans="2:7" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B45" s="12" t="s">
+        <v>2728</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="47" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B47" s="16" t="s">
         <v>2729</v>
       </c>
-    </row>
-    <row r="45" spans="2:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B46" s="16" t="s">
+      <c r="C47" s="22" t="s">
+        <v>2713</v>
+      </c>
+      <c r="D47" s="22" t="s">
         <v>2730</v>
       </c>
-      <c r="C46" s="22" t="s">
-        <v>2713</v>
-      </c>
-      <c r="D46" s="22" t="s">
+      <c r="E47" s="22" t="s">
         <v>2731</v>
       </c>
-      <c r="E46" s="22" t="s">
+      <c r="F47" s="22" t="s">
         <v>2732</v>
       </c>
-      <c r="F46" s="22" t="s">
+      <c r="G47" s="23" t="s">
         <v>2733</v>
-      </c>
-      <c r="G46" s="23" t="s">
-        <v>2734</v>
-      </c>
-    </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B47" s="20" t="s">
-        <v>2735</v>
-      </c>
-      <c r="C47" s="96" t="s">
-        <v>2736</v>
-      </c>
-      <c r="D47" s="24" t="s">
-        <v>2737</v>
-      </c>
-      <c r="E47" s="24">
-        <v>15</v>
-      </c>
-      <c r="F47" s="24">
-        <v>4.1154000000000003E-2</v>
-      </c>
-      <c r="G47" s="25">
-        <v>5.5855E-5</v>
       </c>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B48" s="20" t="s">
-        <v>2738</v>
-      </c>
-      <c r="C48" s="96" t="s">
-        <v>2739</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>2740</v>
-      </c>
-      <c r="E48" s="2">
+        <v>2734</v>
+      </c>
+      <c r="C48" s="95" t="s">
+        <v>2735</v>
+      </c>
+      <c r="D48" s="24" t="s">
+        <v>2736</v>
+      </c>
+      <c r="E48" s="24">
         <v>15</v>
       </c>
-      <c r="F48" s="2">
+      <c r="F48" s="24">
         <v>4.1154000000000003E-2</v>
       </c>
-      <c r="G48" s="65">
+      <c r="G48" s="25">
         <v>5.5855E-5</v>
       </c>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B49" s="20" t="s">
-        <v>2741</v>
-      </c>
-      <c r="C49" s="96" t="s">
-        <v>2742</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>2743</v>
-      </c>
-      <c r="E49" s="3">
+        <v>2737</v>
+      </c>
+      <c r="C49" s="95" t="s">
+        <v>2738</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>2739</v>
+      </c>
+      <c r="E49" s="2">
         <v>15</v>
       </c>
-      <c r="F49" s="59">
+      <c r="F49" s="2">
         <v>4.1154000000000003E-2</v>
       </c>
-      <c r="G49" s="60">
+      <c r="G49" s="65">
         <v>5.5855E-5</v>
       </c>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B50" s="20" t="s">
-        <v>2744</v>
-      </c>
-      <c r="C50" s="96" t="s">
-        <v>2745</v>
-      </c>
-      <c r="D50" s="26" t="s">
-        <v>2746</v>
-      </c>
-      <c r="E50" s="26">
+        <v>2740</v>
+      </c>
+      <c r="C50" s="95" t="s">
+        <v>2741</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>2742</v>
+      </c>
+      <c r="E50" s="3">
         <v>15</v>
       </c>
-      <c r="F50" s="26">
+      <c r="F50" s="59">
         <v>4.1154000000000003E-2</v>
       </c>
-      <c r="G50" s="27">
+      <c r="G50" s="60">
         <v>5.5855E-5</v>
       </c>
     </row>
     <row r="51" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B51" s="20" t="s">
+        <v>2743</v>
+      </c>
+      <c r="C51" s="95" t="s">
+        <v>2744</v>
+      </c>
+      <c r="D51" s="26" t="s">
+        <v>2745</v>
+      </c>
+      <c r="E51" s="26">
+        <v>15</v>
+      </c>
+      <c r="F51" s="26">
+        <v>4.1154000000000003E-2</v>
+      </c>
+      <c r="G51" s="27">
+        <v>5.5855E-5</v>
+      </c>
+    </row>
+    <row r="52" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B52" s="20" t="s">
+        <v>2746</v>
+      </c>
+      <c r="C52" s="95" t="s">
         <v>2747</v>
       </c>
-      <c r="C51" s="96" t="s">
+      <c r="D52" s="1" t="s">
         <v>2748</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="E52" s="1" t="s">
         <v>2749</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="F52" s="1" t="s">
         <v>2750</v>
       </c>
-      <c r="F51" s="1" t="s">
+      <c r="G52" s="69" t="s">
         <v>2751</v>
       </c>
-      <c r="G51" s="69" t="s">
+    </row>
+    <row r="53" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B53" s="96" t="s">
         <v>2752</v>
       </c>
-    </row>
-    <row r="52" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="97" t="s">
+      <c r="C53" s="29" t="s">
         <v>2753</v>
       </c>
-      <c r="C52" s="29" t="s">
+      <c r="D53" s="97" t="s">
         <v>2754</v>
       </c>
-      <c r="D52" s="98" t="s">
+      <c r="E53" s="97" t="s">
         <v>2755</v>
       </c>
-      <c r="E52" s="98" t="s">
+      <c r="F53" s="97" t="s">
         <v>2756</v>
       </c>
-      <c r="F52" s="98" t="s">
+      <c r="G53" s="98" t="s">
         <v>2757</v>
-      </c>
-      <c r="G52" s="99" t="s">
-        <v>2758</v>
       </c>
     </row>
   </sheetData>
@@ -11153,13 +11171,13 @@
     <hyperlink ref="C11" r:id="rId2" xr:uid="{41B7F739-267F-43D4-BA81-097B57D6E931}"/>
     <hyperlink ref="C15" r:id="rId3" xr:uid="{A231AF78-61FF-4A68-B4C3-3DDFEB4B0959}"/>
     <hyperlink ref="C14" r:id="rId4" xr:uid="{5739EB44-C6AF-4C59-923B-AEA8B4D6A45E}"/>
-    <hyperlink ref="B35" location="'Filtered PRODCOM data'!A1" display="'Filtered PRODCOM data'!A1" xr:uid="{10E90DFE-AB5A-4AC1-8DF9-F7272B3062AD}"/>
-    <hyperlink ref="B36" location="'Correlation EU27 2019-2022'!A1" display="'Correlation EU27 2019-2022'!A1" xr:uid="{98A2ACEB-5840-4141-AD9C-D2CBBA86D412}"/>
-    <hyperlink ref="B37" location="'Split Polyamides &amp; Isocyanates'!A1" display="'Split Polyamides &amp; Isocyanates'!A1" xr:uid="{773A090A-19D3-42DC-8B76-7EEDEA334565}"/>
-    <hyperlink ref="B38" location="'End-of-life fates'!A1" display="'End-of-life fates'!A1" xr:uid="{EBC96B5D-3218-48C1-8C4C-720D5912EF5F}"/>
-    <hyperlink ref="B39" location="'Hotspot products export'!A1" display="'Hotspot products export'!A1" xr:uid="{AA5D8B99-4E97-443E-A7C2-70B9BA293EC5}"/>
-    <hyperlink ref="B40" location="'Sensitivity analysis'!A1" display="'Sensitivity analysis'!A1" xr:uid="{7C273249-DB68-46C1-9FB7-62B1EF7CFDEF}"/>
-    <hyperlink ref="B41" location="'References'!A1" display="'References'!A1" xr:uid="{26DE0EC7-BED4-441F-9D61-C78E088A882A}"/>
+    <hyperlink ref="B36" location="'Filtered PRODCOM data'!A1" display="'Filtered PRODCOM data'!A1" xr:uid="{10E90DFE-AB5A-4AC1-8DF9-F7272B3062AD}"/>
+    <hyperlink ref="B37" location="'Correlation EU27 2019-2022'!A1" display="'Correlation EU27 2019-2022'!A1" xr:uid="{98A2ACEB-5840-4141-AD9C-D2CBBA86D412}"/>
+    <hyperlink ref="B38" location="'Split Polyamides &amp; Isocyanates'!A1" display="'Split Polyamides &amp; Isocyanates'!A1" xr:uid="{773A090A-19D3-42DC-8B76-7EEDEA334565}"/>
+    <hyperlink ref="B39" location="'End-of-life fates'!A1" display="'End-of-life fates'!A1" xr:uid="{EBC96B5D-3218-48C1-8C4C-720D5912EF5F}"/>
+    <hyperlink ref="B40" location="'Hotspot products export'!A1" display="'Hotspot products export'!A1" xr:uid="{AA5D8B99-4E97-443E-A7C2-70B9BA293EC5}"/>
+    <hyperlink ref="B41" location="'Sensitivity analysis'!A1" display="'Sensitivity analysis'!A1" xr:uid="{7C273249-DB68-46C1-9FB7-62B1EF7CFDEF}"/>
+    <hyperlink ref="B42" location="'References'!A1" display="'References'!A1" xr:uid="{26DE0EC7-BED4-441F-9D61-C78E088A882A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11175,29 +11193,29 @@
     <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="81" customWidth="1"/>
     <col min="4" max="4" width="42" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="38.5546875" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="40.21875" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="36.77734375" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="38.5546875" customWidth="1"/>
+    <col min="6" max="6" width="40.21875" customWidth="1"/>
+    <col min="7" max="7" width="36.77734375" customWidth="1"/>
     <col min="8" max="8" width="40.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="37" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="37" customWidth="1"/>
     <col min="10" max="10" width="42" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="38.5546875" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="40.21875" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="36.77734375" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="38.5546875" customWidth="1"/>
+    <col min="12" max="12" width="40.21875" customWidth="1"/>
+    <col min="13" max="13" width="36.77734375" customWidth="1"/>
     <col min="14" max="14" width="40.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="37" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="37" customWidth="1"/>
     <col min="16" max="16" width="34.21875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="30.6640625" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="32.5546875" hidden="1" customWidth="1"/>
-    <col min="19" max="19" width="29" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="30.6640625" customWidth="1"/>
+    <col min="18" max="18" width="32.5546875" customWidth="1"/>
+    <col min="19" max="19" width="29" customWidth="1"/>
     <col min="20" max="20" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="29.109375" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="29.109375" customWidth="1"/>
     <col min="22" max="22" width="34.21875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="30.6640625" hidden="1" customWidth="1"/>
-    <col min="24" max="24" width="32.5546875" hidden="1" customWidth="1"/>
-    <col min="25" max="25" width="29" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="30.6640625" customWidth="1"/>
+    <col min="24" max="24" width="32.5546875" customWidth="1"/>
+    <col min="25" max="25" width="29" customWidth="1"/>
     <col min="26" max="26" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="29.109375" hidden="1" customWidth="1"/>
+    <col min="27" max="27" width="29.109375" customWidth="1"/>
     <col min="28" max="28" width="29.5546875" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="20.33203125" style="9" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="29.5546875" bestFit="1" customWidth="1"/>
@@ -11213,10 +11231,10 @@
   <sheetData>
     <row r="1" spans="1:37" s="43" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="11" t="s">
-        <v>3047</v>
-      </c>
-      <c r="B1" s="95" t="s">
-        <v>3050</v>
+        <v>3046</v>
+      </c>
+      <c r="B1" s="94" t="s">
+        <v>3136</v>
       </c>
       <c r="AC1" s="37"/>
       <c r="AE1" s="37"/>
@@ -11226,10 +11244,10 @@
     </row>
     <row r="2" spans="1:37" s="43" customFormat="1" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="11" t="s">
-        <v>3049</v>
+        <v>3048</v>
       </c>
       <c r="B2" s="43" t="s">
-        <v>3051</v>
+        <v>3135</v>
       </c>
       <c r="AC2" s="37"/>
       <c r="AE2" s="37"/>
@@ -11351,7 +11369,7 @@
         <v>2615</v>
       </c>
       <c r="AJ4" s="6" t="s">
-        <v>2796</v>
+        <v>2795</v>
       </c>
       <c r="AK4" s="6" t="s">
         <v>2616</v>
@@ -40231,16 +40249,16 @@
   <sheetData>
     <row r="1" spans="1:4" ht="24" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="11" t="s">
-        <v>3047</v>
-      </c>
-      <c r="B1" s="95" t="s">
-        <v>3102</v>
+        <v>3046</v>
+      </c>
+      <c r="B1" s="94" t="s">
+        <v>3134</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C3" s="85" t="s">
-        <v>3090</v>
+        <v>3084</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -40252,7 +40270,7 @@
         <v>126375890323</v>
       </c>
       <c r="D4" t="s">
-        <v>3089</v>
+        <v>3083</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -40264,12 +40282,12 @@
         <v>120083372330</v>
       </c>
       <c r="D5" s="43" t="s">
-        <v>3089</v>
+        <v>3083</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>3091</v>
+        <v>3085</v>
       </c>
       <c r="C7" s="61" cm="1">
         <f t="array" ref="C7">PEARSON('Filtered PRODCOM data'!AB6:AB237/'Correlation EU27 2019-2022'!C4, 'Filtered PRODCOM data'!AD6:AD237/'Correlation EU27 2019-2022'!C5)</f>
@@ -40295,16 +40313,16 @@
   <sheetData>
     <row r="1" spans="1:5" ht="24" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="11" t="s">
-        <v>3047</v>
-      </c>
-      <c r="B1" s="95" t="s">
-        <v>3052</v>
+        <v>3046</v>
+      </c>
+      <c r="B1" s="94" t="s">
+        <v>3133</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="43" customFormat="1" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B3" s="12" t="s">
-        <v>2845</v>
+        <v>2844</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
@@ -40323,7 +40341,7 @@
         <v>2370412440</v>
       </c>
       <c r="D6" s="46" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -40331,7 +40349,7 @@
     </row>
     <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="38" t="s">
-        <v>2846</v>
+        <v>2845</v>
       </c>
       <c r="D8" s="9"/>
     </row>
@@ -40340,28 +40358,28 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B10" s="36" t="s">
-        <v>2847</v>
+        <v>2846</v>
       </c>
       <c r="C10" s="66">
         <v>1009</v>
       </c>
       <c r="D10" s="46" t="s">
+        <v>2847</v>
+      </c>
+      <c r="E10" s="70" t="s">
         <v>2848</v>
-      </c>
-      <c r="E10" s="70" t="s">
-        <v>2849</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B11" s="36" t="s">
-        <v>2847</v>
+        <v>2846</v>
       </c>
       <c r="C11" s="61">
         <f>C10/1000</f>
         <v>1.0089999999999999</v>
       </c>
       <c r="D11" s="46" t="s">
-        <v>2850</v>
+        <v>2849</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -40372,10 +40390,10 @@
         <v>0.95</v>
       </c>
       <c r="D12" s="46" t="s">
+        <v>2850</v>
+      </c>
+      <c r="E12" s="70" t="s">
         <v>2851</v>
-      </c>
-      <c r="E12" s="70" t="s">
-        <v>2852</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -40387,7 +40405,7 @@
         <v>0.9585499999999999</v>
       </c>
       <c r="D13" s="46" t="s">
-        <v>2850</v>
+        <v>2849</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -40395,16 +40413,16 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B15" s="36" t="s">
-        <v>2853</v>
+        <v>2852</v>
       </c>
       <c r="C15" s="67">
         <v>4</v>
       </c>
       <c r="D15" s="46" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
       <c r="E15" s="70" t="s">
-        <v>2761</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -40412,7 +40430,7 @@
     </row>
     <row r="17" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="38" t="s">
-        <v>2855</v>
+        <v>2854</v>
       </c>
       <c r="D17" s="9"/>
     </row>
@@ -40421,54 +40439,54 @@
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" s="36" t="s">
-        <v>2856</v>
+        <v>2855</v>
       </c>
       <c r="C19" s="66">
         <v>646</v>
       </c>
       <c r="D19" s="46" t="s">
-        <v>2857</v>
+        <v>2856</v>
       </c>
       <c r="E19" s="70" t="s">
-        <v>2849</v>
+        <v>2848</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" s="36" t="s">
-        <v>2858</v>
+        <v>2857</v>
       </c>
       <c r="C20" s="66">
         <v>513</v>
       </c>
       <c r="D20" s="46" t="s">
-        <v>2857</v>
+        <v>2856</v>
       </c>
       <c r="E20" s="70" t="s">
-        <v>2849</v>
+        <v>2848</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" s="36" t="s">
-        <v>2856</v>
+        <v>2855</v>
       </c>
       <c r="C21" s="61">
         <f>C19/1000</f>
         <v>0.64600000000000002</v>
       </c>
       <c r="D21" s="46" t="s">
-        <v>2859</v>
+        <v>2858</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="36" t="s">
-        <v>2858</v>
+        <v>2857</v>
       </c>
       <c r="C22" s="61">
         <f>C20/1000</f>
         <v>0.51300000000000001</v>
       </c>
       <c r="D22" s="46" t="s">
-        <v>2859</v>
+        <v>2858</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.3">
@@ -40476,16 +40494,16 @@
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" s="36" t="s">
-        <v>2860</v>
+        <v>2859</v>
       </c>
       <c r="C24" s="67">
         <v>3.4</v>
       </c>
       <c r="D24" s="46" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
       <c r="E24" s="70" t="s">
-        <v>2761</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.3">
@@ -40503,30 +40521,30 @@
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B28" s="36" t="s">
-        <v>2861</v>
+        <v>2860</v>
       </c>
       <c r="C28" s="67">
         <v>10</v>
       </c>
       <c r="D28" s="63" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
       <c r="E28" s="70" t="s">
-        <v>2763</v>
+        <v>2762</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B29" s="36" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
       <c r="C29" s="67">
         <v>3</v>
       </c>
       <c r="D29" s="63" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
       <c r="E29" s="70" t="s">
-        <v>2763</v>
+        <v>2762</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.3">
@@ -40547,61 +40565,61 @@
         <v>1049281862</v>
       </c>
       <c r="D32" s="46" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
     </row>
     <row r="34" spans="2:5" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B34" s="39" t="s">
-        <v>2863</v>
+        <v>2862</v>
       </c>
     </row>
     <row r="35" spans="2:5" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="36" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C36" t="s">
-        <v>2864</v>
+        <v>2863</v>
       </c>
       <c r="D36" s="64"/>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B37" s="36" t="s">
-        <v>2865</v>
+        <v>2864</v>
       </c>
       <c r="C37" s="67">
         <v>12.010999999999999</v>
       </c>
       <c r="D37" s="46" t="s">
+        <v>2865</v>
+      </c>
+      <c r="E37" s="70" t="s">
         <v>2866</v>
-      </c>
-      <c r="E37" s="70" t="s">
-        <v>2867</v>
       </c>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B38" s="36" t="s">
-        <v>2868</v>
+        <v>2867</v>
       </c>
       <c r="C38" s="67">
         <v>15.999000000000001</v>
       </c>
       <c r="D38" s="46" t="s">
+        <v>2865</v>
+      </c>
+      <c r="E38" s="70" t="s">
         <v>2866</v>
-      </c>
-      <c r="E38" s="70" t="s">
-        <v>2867</v>
       </c>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B39" s="36" t="s">
-        <v>2869</v>
+        <v>2868</v>
       </c>
       <c r="C39" s="67">
         <v>1.008</v>
       </c>
       <c r="D39" s="46" t="s">
-        <v>2866</v>
+        <v>2865</v>
       </c>
       <c r="E39" s="70" t="s">
-        <v>2870</v>
+        <v>2869</v>
       </c>
     </row>
   </sheetData>
@@ -40623,320 +40641,320 @@
   <sheetData>
     <row r="1" spans="1:9" ht="24" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="11" t="s">
-        <v>3047</v>
-      </c>
-      <c r="B1" s="95" t="s">
-        <v>3113</v>
+        <v>3046</v>
+      </c>
+      <c r="B1" s="94" t="s">
+        <v>3132</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="43" customFormat="1" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:9" s="43" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>3104</v>
+        <v>3095</v>
       </c>
       <c r="C4" s="66">
         <v>353</v>
       </c>
       <c r="D4" s="64" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>3118</v>
+        <v>3108</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>3105</v>
+        <v>3096</v>
       </c>
       <c r="C6" s="66">
         <v>55</v>
       </c>
       <c r="D6" s="64" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>3118</v>
+        <v>3108</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>3106</v>
+        <v>3097</v>
       </c>
       <c r="C7" s="66">
         <v>22</v>
       </c>
       <c r="D7" s="64" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>3118</v>
+        <v>3108</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="43" customFormat="1" x14ac:dyDescent="0.3">
       <c r="H8" s="43" t="s">
-        <v>3121</v>
+        <v>3111</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="43" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C9" s="43" t="s">
-        <v>3116</v>
+        <v>3106</v>
       </c>
       <c r="F9" t="s">
-        <v>3115</v>
+        <v>3105</v>
       </c>
       <c r="H9" s="43" t="s">
-        <v>3120</v>
+        <v>3110</v>
       </c>
       <c r="I9" s="43" t="s">
-        <v>3122</v>
+        <v>3112</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="43" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="43" t="s">
-        <v>3119</v>
+        <v>3109</v>
       </c>
       <c r="C10" s="61">
         <f>C6-C7</f>
         <v>33</v>
       </c>
       <c r="D10" s="64" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
       <c r="F10" s="92">
         <f t="shared" ref="F10:F16" si="0">C10/$C$4</f>
         <v>9.3484419263456089E-2</v>
       </c>
       <c r="G10" s="43" t="s">
-        <v>3117</v>
+        <v>3107</v>
       </c>
       <c r="H10" s="42" t="s">
-        <v>3123</v>
+        <v>3113</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>3107</v>
+        <v>3098</v>
       </c>
       <c r="C11" s="66">
         <v>6</v>
       </c>
       <c r="D11" s="64" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>3118</v>
+        <v>3108</v>
       </c>
       <c r="F11" s="92">
         <f t="shared" si="0"/>
         <v>1.69971671388102E-2</v>
       </c>
       <c r="G11" s="43" t="s">
-        <v>3117</v>
+        <v>3107</v>
       </c>
       <c r="H11" s="42" t="s">
-        <v>3124</v>
+        <v>3114</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>3108</v>
+        <v>3099</v>
       </c>
       <c r="C12" s="66">
         <v>13</v>
       </c>
       <c r="D12" s="64" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>3118</v>
+        <v>3108</v>
       </c>
       <c r="F12" s="92">
         <f t="shared" si="0"/>
         <v>3.6827195467422094E-2</v>
       </c>
       <c r="G12" s="43" t="s">
-        <v>3117</v>
+        <v>3107</v>
       </c>
       <c r="H12" s="42" t="s">
-        <v>3124</v>
+        <v>3114</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>3109</v>
+        <v>3100</v>
       </c>
       <c r="C13" s="66">
         <v>26</v>
       </c>
       <c r="D13" s="64" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>3118</v>
+        <v>3108</v>
       </c>
       <c r="F13" s="92">
         <f t="shared" si="0"/>
         <v>7.3654390934844188E-2</v>
       </c>
       <c r="G13" s="43" t="s">
-        <v>3117</v>
+        <v>3107</v>
       </c>
       <c r="H13" s="42" t="s">
-        <v>3125</v>
+        <v>3115</v>
       </c>
       <c r="I13" s="93" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>3110</v>
+        <v>3101</v>
       </c>
       <c r="C14" s="66">
         <v>34</v>
       </c>
       <c r="D14" s="64" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>3118</v>
+        <v>3108</v>
       </c>
       <c r="F14" s="92">
         <f t="shared" si="0"/>
         <v>9.6317280453257784E-2</v>
       </c>
       <c r="G14" s="43" t="s">
-        <v>3117</v>
+        <v>3107</v>
       </c>
       <c r="H14" s="42" t="s">
-        <v>3126</v>
+        <v>3116</v>
       </c>
       <c r="I14" s="93" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>3111</v>
+        <v>3102</v>
       </c>
       <c r="C15" s="66">
         <v>174</v>
       </c>
       <c r="D15" s="64" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>3118</v>
+        <v>3108</v>
       </c>
       <c r="F15" s="92">
         <f t="shared" si="0"/>
         <v>0.49291784702549574</v>
       </c>
       <c r="G15" s="43" t="s">
+        <v>3107</v>
+      </c>
+      <c r="H15" s="42" t="s">
         <v>3117</v>
       </c>
-      <c r="H15" s="42" t="s">
-        <v>3127</v>
-      </c>
       <c r="I15" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>3112</v>
+        <v>3103</v>
       </c>
       <c r="C16" s="66">
         <v>67</v>
       </c>
       <c r="D16" s="64" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>3118</v>
+        <v>3108</v>
       </c>
       <c r="F16" s="92">
         <f t="shared" si="0"/>
         <v>0.18980169971671387</v>
       </c>
       <c r="G16" s="43" t="s">
-        <v>3117</v>
+        <v>3107</v>
       </c>
       <c r="H16" s="42" t="s">
-        <v>3128</v>
+        <v>3118</v>
       </c>
       <c r="I16" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>3114</v>
+        <v>3104</v>
       </c>
       <c r="C18" s="61">
         <f>SUM(C10:C16)</f>
         <v>353</v>
       </c>
       <c r="D18" s="64" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>3118</v>
+        <v>3108</v>
       </c>
       <c r="F18" s="92">
         <f>SUM(F10:F16)</f>
         <v>1</v>
       </c>
       <c r="G18" s="43" t="s">
-        <v>3117</v>
+        <v>3107</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
-        <v>3131</v>
+        <v>3121</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>3129</v>
+        <v>3119</v>
       </c>
       <c r="C22" s="66">
         <v>0.748</v>
       </c>
       <c r="D22" t="s">
-        <v>3089</v>
+        <v>3083</v>
       </c>
       <c r="E22" s="70" t="s">
-        <v>3133</v>
+        <v>3123</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>3130</v>
+        <v>3120</v>
       </c>
       <c r="C23" s="66">
         <v>0.748</v>
       </c>
       <c r="D23" s="43" t="s">
-        <v>3089</v>
+        <v>3083</v>
       </c>
       <c r="E23" s="70" t="s">
-        <v>3133</v>
+        <v>3123</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
-        <v>3132</v>
+        <v>3122</v>
       </c>
       <c r="C24" s="66">
         <v>0.84699999999999998</v>
       </c>
       <c r="D24" s="43" t="s">
-        <v>3089</v>
+        <v>3083</v>
       </c>
       <c r="E24" s="70" t="s">
-        <v>3133</v>
+        <v>3123</v>
       </c>
     </row>
   </sheetData>
@@ -40972,148 +40990,148 @@
   <sheetData>
     <row r="1" spans="1:31" ht="24" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="11" t="s">
-        <v>3047</v>
-      </c>
-      <c r="B1" s="95" t="s">
-        <v>3061</v>
+        <v>3046</v>
+      </c>
+      <c r="B1" s="94" t="s">
+        <v>3131</v>
       </c>
     </row>
     <row r="2" spans="1:31" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="11" t="s">
-        <v>3049</v>
-      </c>
-      <c r="B2" s="43" t="s">
-        <v>3056</v>
+        <v>3048</v>
+      </c>
+      <c r="B2" s="100" t="s">
+        <v>3130</v>
       </c>
     </row>
     <row r="3" spans="1:31" s="43" customFormat="1" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:31" s="43" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="80" t="s">
-        <v>3063</v>
+        <v>3057</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>3065</v>
+        <v>3059</v>
       </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5" s="81" t="s">
+        <v>3053</v>
+      </c>
+      <c r="B5" t="s">
         <v>3058</v>
-      </c>
-      <c r="B5" t="s">
-        <v>3064</v>
       </c>
     </row>
     <row r="6" spans="1:31" s="43" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="82" t="s">
-        <v>3066</v>
+        <v>3060</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>3067</v>
+        <v>3061</v>
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="F7" s="94" t="s">
+      <c r="F7" s="99" t="s">
         <v>705</v>
       </c>
-      <c r="G7" s="94"/>
+      <c r="G7" s="99"/>
       <c r="I7" s="40" t="s">
-        <v>3062</v>
+        <v>3056</v>
       </c>
       <c r="J7" s="40"/>
     </row>
     <row r="8" spans="1:31" s="14" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A8" s="78" t="s">
+        <v>3043</v>
+      </c>
+      <c r="B8" s="79" t="s">
+        <v>2870</v>
+      </c>
+      <c r="C8" s="78" t="s">
+        <v>2796</v>
+      </c>
+      <c r="D8" s="50" t="s">
+        <v>2871</v>
+      </c>
+      <c r="E8" s="50" t="s">
+        <v>2872</v>
+      </c>
+      <c r="F8" s="50" t="s">
+        <v>3020</v>
+      </c>
+      <c r="G8" s="50" t="s">
+        <v>3021</v>
+      </c>
+      <c r="H8" s="78" t="s">
         <v>3044</v>
       </c>
-      <c r="B8" s="79" t="s">
-        <v>2871</v>
-      </c>
-      <c r="C8" s="78" t="s">
-        <v>2797</v>
-      </c>
-      <c r="D8" s="50" t="s">
-        <v>2872</v>
-      </c>
-      <c r="E8" s="50" t="s">
-        <v>2873</v>
-      </c>
-      <c r="F8" s="50" t="s">
-        <v>3021</v>
-      </c>
-      <c r="G8" s="50" t="s">
-        <v>3022</v>
-      </c>
-      <c r="H8" s="78" t="s">
-        <v>3045</v>
-      </c>
       <c r="I8" s="78" t="s">
-        <v>3057</v>
+        <v>3052</v>
       </c>
       <c r="J8" s="50" t="s">
         <v>2617</v>
       </c>
       <c r="K8" s="50" t="s">
+        <v>2873</v>
+      </c>
+      <c r="L8" s="50" t="s">
         <v>2874</v>
       </c>
-      <c r="L8" s="50" t="s">
+      <c r="M8" s="50" t="s">
         <v>2875</v>
       </c>
-      <c r="M8" s="50" t="s">
+      <c r="N8" s="50" t="s">
         <v>2876</v>
       </c>
-      <c r="N8" s="50" t="s">
+      <c r="O8" s="55" t="s">
         <v>2877</v>
       </c>
-      <c r="O8" s="55" t="s">
-        <v>2878</v>
-      </c>
       <c r="P8" s="50" t="s">
+        <v>3022</v>
+      </c>
+      <c r="Q8" s="50" t="s">
         <v>3023</v>
       </c>
-      <c r="Q8" s="50" t="s">
-        <v>3024</v>
-      </c>
       <c r="R8" s="50" t="s">
+        <v>3025</v>
+      </c>
+      <c r="S8" s="50" t="s">
         <v>3026</v>
       </c>
-      <c r="S8" s="50" t="s">
+      <c r="T8" s="50" t="s">
+        <v>3035</v>
+      </c>
+      <c r="U8" s="55" t="s">
+        <v>3036</v>
+      </c>
+      <c r="V8" s="50" t="s">
+        <v>3028</v>
+      </c>
+      <c r="W8" s="50" t="s">
+        <v>3029</v>
+      </c>
+      <c r="X8" s="50" t="s">
         <v>3027</v>
       </c>
-      <c r="T8" s="50" t="s">
-        <v>3036</v>
-      </c>
-      <c r="U8" s="55" t="s">
+      <c r="Y8" s="50" t="s">
+        <v>3033</v>
+      </c>
+      <c r="Z8" s="50" t="s">
         <v>3037</v>
       </c>
-      <c r="V8" s="50" t="s">
-        <v>3029</v>
-      </c>
-      <c r="W8" s="50" t="s">
-        <v>3030</v>
-      </c>
-      <c r="X8" s="50" t="s">
-        <v>3028</v>
-      </c>
-      <c r="Y8" s="50" t="s">
-        <v>3034</v>
-      </c>
-      <c r="Z8" s="50" t="s">
+      <c r="AA8" s="50" t="s">
         <v>3038</v>
       </c>
-      <c r="AA8" s="50" t="s">
-        <v>3039</v>
-      </c>
       <c r="AB8" s="50" t="s">
+        <v>3040</v>
+      </c>
+      <c r="AC8" s="50" t="s">
         <v>3041</v>
       </c>
-      <c r="AC8" s="50" t="s">
-        <v>3042</v>
-      </c>
       <c r="AD8" s="50" t="s">
-        <v>3054</v>
+        <v>3050</v>
       </c>
       <c r="AE8" s="50" t="s">
-        <v>3055</v>
+        <v>3051</v>
       </c>
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.3">
@@ -41124,13 +41142,13 @@
         <v>614</v>
       </c>
       <c r="C9" s="57" t="s">
-        <v>2798</v>
+        <v>2797</v>
       </c>
       <c r="D9" t="s">
         <v>615</v>
       </c>
       <c r="E9" s="41" t="s">
-        <v>2879</v>
+        <v>2878</v>
       </c>
       <c r="F9" s="49">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B9, prodcom_data[product], 0))</f>
@@ -41151,23 +41169,23 @@
         <v>2642</v>
       </c>
       <c r="K9" s="67" t="s">
-        <v>2880</v>
+        <v>2879</v>
       </c>
       <c r="L9" s="67">
         <v>42.081000000000003</v>
       </c>
       <c r="M9" s="68" t="s">
-        <v>2881</v>
+        <v>2880</v>
       </c>
       <c r="N9" s="62">
         <f>M9*'Split Polyamides &amp; Isocyanates'!$C$37/L9</f>
         <v>0.85627717972481643</v>
       </c>
       <c r="O9" s="69" t="s">
-        <v>2882</v>
+        <v>2881</v>
       </c>
       <c r="P9" s="52" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="Q9" s="51">
         <v>1</v>
@@ -41177,20 +41195,20 @@
       <c r="T9" s="52"/>
       <c r="U9" s="56"/>
       <c r="V9" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="W9" s="51">
         <v>0.89</v>
       </c>
       <c r="X9" s="52" t="s">
-        <v>3084</v>
+        <v>3078</v>
       </c>
       <c r="Y9" s="54">
         <f>0.05+0.01</f>
         <v>6.0000000000000005E-2</v>
       </c>
       <c r="Z9" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="AA9" s="54" cm="1">
         <f t="array" ref="AA9">1-SUM(IF(ISNUMBER(V9:Y9), V9:Y9, 0))</f>
@@ -41209,7 +41227,7 @@
         <v>8</v>
       </c>
       <c r="C10" s="57" t="s">
-        <v>2799</v>
+        <v>2798</v>
       </c>
       <c r="D10" t="s">
         <v>9</v>
@@ -41236,29 +41254,29 @@
         <v>2642</v>
       </c>
       <c r="K10" s="67" t="s">
-        <v>2886</v>
+        <v>2885</v>
       </c>
       <c r="L10" s="67">
         <v>28.05</v>
       </c>
       <c r="M10" s="68" t="s">
-        <v>2887</v>
+        <v>2886</v>
       </c>
       <c r="N10" s="62">
         <f>M10*'Split Polyamides &amp; Isocyanates'!$C$37/L10</f>
         <v>0.85639928698752221</v>
       </c>
       <c r="O10" s="69" t="s">
-        <v>2888</v>
+        <v>2887</v>
       </c>
       <c r="P10" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="Q10" s="51">
         <v>0.96</v>
       </c>
       <c r="R10" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="S10" s="54" cm="1">
         <f t="array" ref="S10">1-SUM(IF(ISNUMBER(P10:Q10), P10:Q10, 0))</f>
@@ -41267,25 +41285,25 @@
       <c r="T10" s="52"/>
       <c r="U10" s="56"/>
       <c r="V10" s="52" t="s">
-        <v>3033</v>
+        <v>3032</v>
       </c>
       <c r="W10" s="51">
         <v>0.94</v>
       </c>
       <c r="X10" s="52" t="s">
-        <v>3085</v>
+        <v>3079</v>
       </c>
       <c r="Y10" s="53">
         <v>0.03</v>
       </c>
       <c r="Z10" s="52" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="AA10" s="53">
         <v>0.02</v>
       </c>
       <c r="AB10" s="52" t="s">
-        <v>3035</v>
+        <v>3034</v>
       </c>
       <c r="AC10" s="53">
         <v>0.01</v>
@@ -41301,13 +41319,13 @@
         <v>11</v>
       </c>
       <c r="C11" s="57" t="s">
-        <v>2799</v>
+        <v>2798</v>
       </c>
       <c r="D11" t="s">
         <v>12</v>
       </c>
       <c r="E11" s="41" t="s">
-        <v>2883</v>
+        <v>2882</v>
       </c>
       <c r="F11" s="49">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B11, prodcom_data[product], 0))</f>
@@ -41328,29 +41346,29 @@
         <v>2642</v>
       </c>
       <c r="K11" s="67" t="s">
-        <v>2884</v>
+        <v>2883</v>
       </c>
       <c r="L11" s="67">
         <v>42.08</v>
       </c>
       <c r="M11" s="68" t="s">
-        <v>2881</v>
+        <v>2880</v>
       </c>
       <c r="N11" s="62">
         <f>M11*'Split Polyamides &amp; Isocyanates'!$C$37/L11</f>
         <v>0.85629752851711038</v>
       </c>
       <c r="O11" s="69" t="s">
-        <v>2885</v>
+        <v>2884</v>
       </c>
       <c r="P11" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="Q11" s="51">
         <v>0.98</v>
       </c>
       <c r="R11" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="S11" s="54" cm="1">
         <f t="array" ref="S11">1-SUM(IF(ISNUMBER(P11:Q11), P11:Q11, 0))</f>
@@ -41359,25 +41377,25 @@
       <c r="T11" s="52"/>
       <c r="U11" s="56"/>
       <c r="V11" s="52" t="s">
-        <v>3033</v>
+        <v>3032</v>
       </c>
       <c r="W11" s="51">
         <v>0.97</v>
       </c>
       <c r="X11" s="52" t="s">
-        <v>3085</v>
+        <v>3079</v>
       </c>
       <c r="Y11" s="53">
         <v>0.01</v>
       </c>
       <c r="Z11" s="52" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="AA11" s="53">
         <v>0.01</v>
       </c>
       <c r="AB11" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="AC11" s="54" cm="1">
         <f t="array" ref="AC11">1-SUM(IF(ISNUMBER(V11:AA11), V11:AA11, 0))</f>
@@ -41394,13 +41412,13 @@
         <v>539</v>
       </c>
       <c r="C12" s="57" t="s">
-        <v>2800</v>
+        <v>2799</v>
       </c>
       <c r="D12" t="s">
         <v>540</v>
       </c>
       <c r="E12" s="41" t="s">
-        <v>2889</v>
+        <v>2888</v>
       </c>
       <c r="F12" s="49">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B12, prodcom_data[product], 0))</f>
@@ -41421,23 +41439,23 @@
         <v>2642</v>
       </c>
       <c r="K12" s="67" t="s">
-        <v>2890</v>
+        <v>2889</v>
       </c>
       <c r="L12" s="67">
         <v>28.053999999999998</v>
       </c>
       <c r="M12" s="68" t="s">
-        <v>2887</v>
+        <v>2886</v>
       </c>
       <c r="N12" s="62">
         <f>M12*'Split Polyamides &amp; Isocyanates'!$C$37/L12</f>
         <v>0.85627717972481643</v>
       </c>
       <c r="O12" s="69" t="s">
-        <v>2891</v>
+        <v>2890</v>
       </c>
       <c r="P12" s="52" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="Q12" s="51">
         <v>1</v>
@@ -41447,19 +41465,19 @@
       <c r="T12" s="52"/>
       <c r="U12" s="56"/>
       <c r="V12" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="W12" s="51">
         <v>0.81</v>
       </c>
       <c r="X12" s="52" t="s">
-        <v>3035</v>
+        <v>3034</v>
       </c>
       <c r="Y12" s="53">
         <v>0.05</v>
       </c>
       <c r="Z12" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="AA12" s="54" cm="1">
         <f t="array" ref="AA12">1-SUM(IF(ISNUMBER(V12:Y12), V12:Y12, 0))</f>
@@ -41478,13 +41496,13 @@
         <v>111</v>
       </c>
       <c r="C13" s="77" t="s">
-        <v>3053</v>
+        <v>3049</v>
       </c>
       <c r="D13" t="s">
         <v>112</v>
       </c>
       <c r="E13" s="41" t="s">
-        <v>2892</v>
+        <v>2891</v>
       </c>
       <c r="F13" s="49">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B13, prodcom_data[product], 0))</f>
@@ -41505,66 +41523,66 @@
         <v>2642</v>
       </c>
       <c r="K13" s="67" t="s">
-        <v>2893</v>
+        <v>2892</v>
       </c>
       <c r="L13" s="67">
         <v>32.042000000000002</v>
       </c>
       <c r="M13" s="68" t="s">
-        <v>2894</v>
+        <v>2893</v>
       </c>
       <c r="N13" s="62">
         <f>M13*'Split Polyamides &amp; Isocyanates'!$C$37/L13</f>
         <v>0.3748517570688471</v>
       </c>
       <c r="O13" s="69" t="s">
-        <v>2895</v>
+        <v>2894</v>
       </c>
       <c r="P13" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="Q13" s="51">
         <v>0.35</v>
       </c>
       <c r="R13" s="52" t="s">
-        <v>3035</v>
+        <v>3034</v>
       </c>
       <c r="S13" s="51">
         <v>0.23</v>
       </c>
       <c r="T13" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="U13" s="54">
         <f>1-Q13-S13</f>
         <v>0.42000000000000004</v>
       </c>
       <c r="V13" s="52" t="s">
-        <v>3033</v>
+        <v>3032</v>
       </c>
       <c r="W13" s="51">
         <v>0.18</v>
       </c>
       <c r="X13" s="52" t="s">
-        <v>3040</v>
+        <v>3039</v>
       </c>
       <c r="Y13" s="51">
         <v>0.21</v>
       </c>
       <c r="Z13" s="52" t="s">
-        <v>3035</v>
+        <v>3034</v>
       </c>
       <c r="AA13" s="51">
         <v>0.23</v>
       </c>
       <c r="AB13" s="52" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="AC13" s="53">
         <v>0.16</v>
       </c>
       <c r="AD13" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="AE13" s="54" cm="1">
         <f t="array" ref="AE13">1-SUM(IF(ISNUMBER(V13:AC13), V13:AC13, 0))</f>
@@ -41579,7 +41597,7 @@
         <v>34</v>
       </c>
       <c r="C14" s="57" t="s">
-        <v>2802</v>
+        <v>2801</v>
       </c>
       <c r="D14" t="s">
         <v>35</v>
@@ -41606,29 +41624,29 @@
         <v>2642</v>
       </c>
       <c r="K14" s="67" t="s">
-        <v>2896</v>
+        <v>2895</v>
       </c>
       <c r="L14" s="67">
         <v>78.11</v>
       </c>
       <c r="M14" s="68" t="s">
-        <v>2897</v>
+        <v>2896</v>
       </c>
       <c r="N14" s="62">
         <f>M14*'Split Polyamides &amp; Isocyanates'!$C$37/L14</f>
         <v>0.92262194341313541</v>
       </c>
       <c r="O14" s="69" t="s">
-        <v>2898</v>
+        <v>2897</v>
       </c>
       <c r="P14" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="Q14" s="51">
         <v>0.93</v>
       </c>
       <c r="R14" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="S14" s="54" cm="1">
         <f t="array" ref="S14">1-SUM(IF(ISNUMBER(P14:Q14), P14:Q14, 0))</f>
@@ -41637,13 +41655,13 @@
       <c r="T14" s="52"/>
       <c r="U14" s="56"/>
       <c r="V14" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="W14" s="51">
         <v>0.93</v>
       </c>
       <c r="X14" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="Y14" s="54" cm="1">
         <f t="array" ref="Y14">1-SUM(IF(ISNUMBER(V14:W14), V14:W14, 0))</f>
@@ -41664,13 +41682,13 @@
         <v>563</v>
       </c>
       <c r="C15" s="57" t="s">
-        <v>2803</v>
+        <v>2802</v>
       </c>
       <c r="D15" t="s">
         <v>564</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>2899</v>
+        <v>2898</v>
       </c>
       <c r="F15" s="49">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B15, prodcom_data[product], 0))</f>
@@ -41691,29 +41709,29 @@
         <v>2642</v>
       </c>
       <c r="K15" s="67" t="s">
-        <v>2900</v>
+        <v>2899</v>
       </c>
       <c r="L15" s="67">
         <v>62.5</v>
       </c>
       <c r="M15" s="68" t="s">
-        <v>2887</v>
+        <v>2886</v>
       </c>
       <c r="N15" s="62">
         <f>M15*'Split Polyamides &amp; Isocyanates'!$C$37/L15</f>
         <v>0.38435199999999997</v>
       </c>
       <c r="O15" s="69" t="s">
-        <v>2901</v>
+        <v>2900</v>
       </c>
       <c r="P15" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="Q15" s="51">
         <v>0.92</v>
       </c>
       <c r="R15" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="S15" s="54" cm="1">
         <f t="array" ref="S15">1-SUM(IF(ISNUMBER(P15:Q15), P15:Q15, 0))</f>
@@ -41722,20 +41740,20 @@
       <c r="T15" s="52"/>
       <c r="U15" s="56"/>
       <c r="V15" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="W15" s="51">
         <v>0.92</v>
       </c>
       <c r="X15" s="52" t="s">
-        <v>3086</v>
+        <v>3080</v>
       </c>
       <c r="Y15" s="54">
         <f>0.03+0.03</f>
         <v>0.06</v>
       </c>
       <c r="Z15" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="AA15" s="54" cm="1">
         <f t="array" ref="AA15">1-SUM(IF(ISNUMBER(V15:Y15), V15:Y15, 0))</f>
@@ -41754,13 +41772,13 @@
         <v>536</v>
       </c>
       <c r="C16" s="57" t="s">
-        <v>2801</v>
+        <v>2800</v>
       </c>
       <c r="D16" t="s">
         <v>537</v>
       </c>
       <c r="E16" s="41" t="s">
-        <v>2889</v>
+        <v>2888</v>
       </c>
       <c r="F16" s="49">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B16, prodcom_data[product], 0))</f>
@@ -41781,23 +41799,23 @@
         <v>2642</v>
       </c>
       <c r="K16" s="67" t="s">
-        <v>2890</v>
+        <v>2889</v>
       </c>
       <c r="L16" s="67">
         <v>28.053999999999998</v>
       </c>
       <c r="M16" s="68" t="s">
-        <v>2887</v>
+        <v>2886</v>
       </c>
       <c r="N16" s="62">
         <f>M16*'Split Polyamides &amp; Isocyanates'!$C$37/L16</f>
         <v>0.85627717972481643</v>
       </c>
       <c r="O16" s="69" t="s">
-        <v>2891</v>
+        <v>2890</v>
       </c>
       <c r="P16" s="52" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="Q16" s="51">
         <v>1</v>
@@ -41807,19 +41825,19 @@
       <c r="T16" s="52"/>
       <c r="U16" s="56"/>
       <c r="V16" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="W16" s="51">
         <v>0.84</v>
       </c>
       <c r="X16" s="52" t="s">
-        <v>3035</v>
+        <v>3034</v>
       </c>
       <c r="Y16" s="53">
         <v>0.04</v>
       </c>
       <c r="Z16" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="AA16" s="54" cm="1">
         <f t="array" ref="AA16">1-SUM(IF(ISNUMBER(V16:Y16), V16:Y16, 0))</f>
@@ -41838,13 +41856,13 @@
         <v>533</v>
       </c>
       <c r="C17" s="57" t="s">
-        <v>2801</v>
+        <v>2800</v>
       </c>
       <c r="D17" t="s">
         <v>534</v>
       </c>
       <c r="E17" s="41" t="s">
-        <v>2889</v>
+        <v>2888</v>
       </c>
       <c r="F17" s="49">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B17, prodcom_data[product], 0))</f>
@@ -41865,23 +41883,23 @@
         <v>2642</v>
       </c>
       <c r="K17" s="67" t="s">
-        <v>2890</v>
+        <v>2889</v>
       </c>
       <c r="L17" s="67">
         <v>28.053999999999998</v>
       </c>
       <c r="M17" s="68" t="s">
-        <v>2887</v>
+        <v>2886</v>
       </c>
       <c r="N17" s="62">
         <f>M17*'Split Polyamides &amp; Isocyanates'!$C$37/L17</f>
         <v>0.85627717972481643</v>
       </c>
       <c r="O17" s="69" t="s">
-        <v>2891</v>
+        <v>2890</v>
       </c>
       <c r="P17" s="52" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="Q17" s="51">
         <v>1</v>
@@ -41891,7 +41909,7 @@
       <c r="T17" s="52"/>
       <c r="U17" s="56"/>
       <c r="V17" s="52" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="W17" s="51">
         <v>1</v>
@@ -41913,7 +41931,7 @@
         <v>49</v>
       </c>
       <c r="C18" s="57" t="s">
-        <v>2804</v>
+        <v>2803</v>
       </c>
       <c r="D18" t="s">
         <v>50</v>
@@ -41940,29 +41958,29 @@
         <v>2642</v>
       </c>
       <c r="K18" s="67" t="s">
-        <v>2910</v>
+        <v>2909</v>
       </c>
       <c r="L18" s="67">
         <v>104.15</v>
       </c>
       <c r="M18" s="68" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="N18" s="62">
         <f>M18*'Split Polyamides &amp; Isocyanates'!$C$37/L18</f>
         <v>0.92259241478636567</v>
       </c>
       <c r="O18" s="69" t="s">
-        <v>2911</v>
+        <v>2910</v>
       </c>
       <c r="P18" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="Q18" s="51">
         <v>0.84</v>
       </c>
       <c r="R18" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="S18" s="54" cm="1">
         <f t="array" ref="S18">1-SUM(IF(ISNUMBER(P18:Q18), P18:Q18, 0))</f>
@@ -41971,25 +41989,25 @@
       <c r="T18" s="52"/>
       <c r="U18" s="56"/>
       <c r="V18" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="W18" s="51">
         <v>0.84</v>
       </c>
       <c r="X18" s="52" t="s">
-        <v>3035</v>
+        <v>3034</v>
       </c>
       <c r="Y18" s="53">
         <v>0.06</v>
       </c>
       <c r="Z18" s="52" t="s">
-        <v>3087</v>
+        <v>3081</v>
       </c>
       <c r="AA18" s="53">
         <v>0.03</v>
       </c>
       <c r="AB18" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="AC18" s="54" cm="1">
         <f t="array" ref="AC18">1-SUM(IF(ISNUMBER(V18:AA18), V18:AA18, 0))</f>
@@ -42006,13 +42024,13 @@
         <v>263</v>
       </c>
       <c r="C19" s="57" t="s">
-        <v>2805</v>
+        <v>2804</v>
       </c>
       <c r="D19" t="s">
         <v>264</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>2902</v>
+        <v>2901</v>
       </c>
       <c r="F19" s="49">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B19, prodcom_data[product], 0))</f>
@@ -42033,23 +42051,23 @@
         <v>2656</v>
       </c>
       <c r="K19" s="67" t="s">
-        <v>2903</v>
+        <v>2902</v>
       </c>
       <c r="L19" s="67">
         <v>166.13</v>
       </c>
       <c r="M19" s="68" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="N19" s="62">
         <f>M19*'Split Polyamides &amp; Isocyanates'!$C$37/L19</f>
         <v>0.57839041714320105</v>
       </c>
       <c r="O19" s="69" t="s">
-        <v>2905</v>
+        <v>2904</v>
       </c>
       <c r="P19" s="52" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="Q19" s="51">
         <v>1</v>
@@ -42059,7 +42077,7 @@
       <c r="T19" s="52"/>
       <c r="U19" s="56"/>
       <c r="V19" s="52" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="W19" s="51">
         <v>1</v>
@@ -42081,13 +42099,13 @@
         <v>599</v>
       </c>
       <c r="C20" s="57" t="s">
-        <v>2806</v>
+        <v>2805</v>
       </c>
       <c r="D20" t="s">
         <v>600</v>
       </c>
       <c r="E20" s="41" t="s">
-        <v>2906</v>
+        <v>2905</v>
       </c>
       <c r="F20" s="49">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B20, prodcom_data[product], 0))</f>
@@ -42108,23 +42126,23 @@
         <v>2642</v>
       </c>
       <c r="K20" s="67" t="s">
-        <v>2907</v>
+        <v>2906</v>
       </c>
       <c r="L20" s="67">
         <v>222.24</v>
       </c>
       <c r="M20" s="68" t="s">
-        <v>2908</v>
+        <v>2907</v>
       </c>
       <c r="N20" s="62">
         <f>M20*'Split Polyamides &amp; Isocyanates'!$C$37/L20</f>
         <v>0.64854211663066952</v>
       </c>
       <c r="O20" s="69" t="s">
-        <v>2909</v>
+        <v>2908</v>
       </c>
       <c r="P20" s="52" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="Q20" s="51">
         <v>1</v>
@@ -42134,7 +42152,7 @@
       <c r="T20" s="52"/>
       <c r="U20" s="56"/>
       <c r="V20" s="52" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="W20" s="51">
         <v>1</v>
@@ -42156,13 +42174,13 @@
         <v>17</v>
       </c>
       <c r="C21" s="57" t="s">
-        <v>2807</v>
+        <v>2806</v>
       </c>
       <c r="D21" t="s">
         <v>18</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>2912</v>
+        <v>2911</v>
       </c>
       <c r="F21" s="49">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B21, prodcom_data[product], 0))</f>
@@ -42183,23 +42201,23 @@
         <v>2660</v>
       </c>
       <c r="K21" s="67" t="s">
-        <v>2913</v>
+        <v>2912</v>
       </c>
       <c r="L21" s="67">
         <v>54.09</v>
       </c>
       <c r="M21" s="68" t="s">
-        <v>2914</v>
+        <v>2913</v>
       </c>
       <c r="N21" s="62">
         <f>M21*'Split Polyamides &amp; Isocyanates'!$C$37/L21</f>
         <v>0.88822333148456267</v>
       </c>
       <c r="O21" s="69" t="s">
-        <v>2915</v>
+        <v>2914</v>
       </c>
       <c r="P21" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="Q21" s="51">
         <v>1</v>
@@ -42209,7 +42227,7 @@
       <c r="T21" s="52"/>
       <c r="U21" s="56"/>
       <c r="V21" s="52" t="s">
-        <v>3033</v>
+        <v>3032</v>
       </c>
       <c r="W21" s="51">
         <v>1</v>
@@ -42231,13 +42249,13 @@
         <v>14</v>
       </c>
       <c r="C22" s="57" t="s">
-        <v>2809</v>
+        <v>2808</v>
       </c>
       <c r="D22" t="s">
         <v>15</v>
       </c>
       <c r="E22" s="41" t="s">
-        <v>2916</v>
+        <v>2915</v>
       </c>
       <c r="F22" s="49">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B22, prodcom_data[product], 0))</f>
@@ -42258,23 +42276,23 @@
         <v>2642</v>
       </c>
       <c r="K22" s="67" t="s">
-        <v>2917</v>
+        <v>2916</v>
       </c>
       <c r="L22" s="67">
         <v>112.21</v>
       </c>
       <c r="M22" s="68" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="N22" s="62">
         <f>M22*'Split Polyamides &amp; Isocyanates'!$C$37/L22</f>
         <v>0.85632296586756973</v>
       </c>
       <c r="O22" s="69" t="s">
-        <v>2918</v>
+        <v>2917</v>
       </c>
       <c r="P22" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="Q22" s="51">
         <v>1</v>
@@ -42284,7 +42302,7 @@
       <c r="T22" s="52"/>
       <c r="U22" s="56"/>
       <c r="V22" s="52" t="s">
-        <v>3033</v>
+        <v>3032</v>
       </c>
       <c r="W22" s="51">
         <v>1</v>
@@ -42306,13 +42324,13 @@
         <v>548</v>
       </c>
       <c r="C23" s="57" t="s">
-        <v>2810</v>
+        <v>2809</v>
       </c>
       <c r="D23" t="s">
         <v>549</v>
       </c>
       <c r="E23" s="41" t="s">
-        <v>2919</v>
+        <v>2918</v>
       </c>
       <c r="F23" s="49">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B23, prodcom_data[product], 0))</f>
@@ -42333,23 +42351,23 @@
         <v>2642</v>
       </c>
       <c r="K23" s="67" t="s">
-        <v>2920</v>
+        <v>2919</v>
       </c>
       <c r="L23" s="67">
         <v>104.15199999999999</v>
       </c>
       <c r="M23" s="68" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="N23" s="62">
         <f>M23*'Split Polyamides &amp; Isocyanates'!$C$37/L23</f>
         <v>0.92257469851755136</v>
       </c>
       <c r="O23" s="69" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
       <c r="P23" s="52" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="Q23" s="51">
         <v>1</v>
@@ -42359,13 +42377,13 @@
       <c r="T23" s="52"/>
       <c r="U23" s="56"/>
       <c r="V23" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="W23" s="51">
         <v>0.91</v>
       </c>
       <c r="X23" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="Y23" s="54" cm="1">
         <f t="array" ref="Y23">1-SUM(IF(ISNUMBER(V23:W23), V23:W23, 0))</f>
@@ -42386,13 +42404,13 @@
         <v>132</v>
       </c>
       <c r="C24" s="57" t="s">
-        <v>2811</v>
+        <v>2810</v>
       </c>
       <c r="D24" t="s">
         <v>133</v>
       </c>
       <c r="E24" s="41" t="s">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="F24" s="49">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B24, prodcom_data[product], 0))</f>
@@ -42413,29 +42431,29 @@
         <v>2642</v>
       </c>
       <c r="K24" s="67" t="s">
-        <v>2926</v>
+        <v>2925</v>
       </c>
       <c r="L24" s="67">
         <v>62.07</v>
       </c>
       <c r="M24" s="68" t="s">
-        <v>2887</v>
+        <v>2886</v>
       </c>
       <c r="N24" s="62">
         <f>M24*'Split Polyamides &amp; Isocyanates'!$C$37/L24</f>
         <v>0.38701466086676328</v>
       </c>
       <c r="O24" s="69" t="s">
-        <v>2927</v>
+        <v>2926</v>
       </c>
       <c r="P24" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="Q24" s="53">
         <v>0.56000000000000005</v>
       </c>
       <c r="R24" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="S24" s="54" cm="1">
         <f t="array" ref="S24">1-SUM(IF(ISNUMBER(P24:Q24), P24:Q24, 0))</f>
@@ -42444,13 +42462,13 @@
       <c r="T24" s="52"/>
       <c r="U24" s="56"/>
       <c r="V24" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="W24" s="53">
         <v>0.56000000000000005</v>
       </c>
       <c r="X24" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="Y24" s="54" cm="1">
         <f t="array" ref="Y24">1-SUM(IF(ISNUMBER(V24:W24), V24:W24, 0))</f>
@@ -42471,13 +42489,13 @@
         <v>476</v>
       </c>
       <c r="C25" s="57" t="s">
-        <v>2812</v>
+        <v>2811</v>
       </c>
       <c r="D25" t="s">
         <v>477</v>
       </c>
       <c r="E25" s="41" t="s">
-        <v>2922</v>
+        <v>2921</v>
       </c>
       <c r="F25" s="49">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B25, prodcom_data[product], 0))</f>
@@ -42498,29 +42516,29 @@
         <v>2642</v>
       </c>
       <c r="K25" s="67" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
       <c r="L25" s="67">
         <v>58.08</v>
       </c>
       <c r="M25" s="68" t="s">
-        <v>2881</v>
+        <v>2880</v>
       </c>
       <c r="N25" s="62">
         <f>M25*'Split Polyamides &amp; Isocyanates'!$C$37/L25</f>
         <v>0.62040289256198355</v>
       </c>
       <c r="O25" s="69" t="s">
-        <v>2924</v>
+        <v>2923</v>
       </c>
       <c r="P25" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="Q25" s="51">
         <v>0.98</v>
       </c>
       <c r="R25" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="S25" s="54" cm="1">
         <f t="array" ref="S25">1-SUM(IF(ISNUMBER(P25:Q25), P25:Q25, 0))</f>
@@ -42529,13 +42547,13 @@
       <c r="T25" s="52"/>
       <c r="U25" s="56"/>
       <c r="V25" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="W25" s="51">
         <v>0.98</v>
       </c>
       <c r="X25" s="52" t="s">
-        <v>3035</v>
+        <v>3034</v>
       </c>
       <c r="Y25" s="53">
         <v>0.02</v>
@@ -42555,13 +42573,13 @@
         <v>551</v>
       </c>
       <c r="C26" s="57" t="s">
-        <v>2813</v>
+        <v>2812</v>
       </c>
       <c r="D26" t="s">
         <v>552</v>
       </c>
       <c r="E26" s="41" t="s">
-        <v>2919</v>
+        <v>2918</v>
       </c>
       <c r="F26" s="49">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B26, prodcom_data[product], 0))</f>
@@ -42582,23 +42600,23 @@
         <v>2642</v>
       </c>
       <c r="K26" s="67" t="s">
-        <v>2920</v>
+        <v>2919</v>
       </c>
       <c r="L26" s="67">
         <v>104.15199999999999</v>
       </c>
       <c r="M26" s="68" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="N26" s="62">
         <f>M26*'Split Polyamides &amp; Isocyanates'!$C$37/L26</f>
         <v>0.92257469851755136</v>
       </c>
       <c r="O26" s="69" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
       <c r="P26" s="52" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="Q26" s="51">
         <v>1</v>
@@ -42608,7 +42626,7 @@
       <c r="T26" s="52"/>
       <c r="U26" s="56"/>
       <c r="V26" s="52" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="W26" s="51">
         <v>1</v>
@@ -42630,13 +42648,13 @@
         <v>72</v>
       </c>
       <c r="C27" s="57" t="s">
-        <v>2814</v>
+        <v>2813</v>
       </c>
       <c r="D27" t="s">
         <v>73</v>
       </c>
       <c r="E27" s="41" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="F27" s="49">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B27, prodcom_data[product], 0))</f>
@@ -42657,29 +42675,29 @@
         <v>2642</v>
       </c>
       <c r="K27" s="67" t="s">
-        <v>2933</v>
+        <v>2932</v>
       </c>
       <c r="L27" s="67">
         <v>98.96</v>
       </c>
       <c r="M27" s="68" t="s">
-        <v>2887</v>
+        <v>2886</v>
       </c>
       <c r="N27" s="62">
         <f>M27*'Split Polyamides &amp; Isocyanates'!$C$37/L27</f>
         <v>0.24274454324979791</v>
       </c>
       <c r="O27" s="69" t="s">
-        <v>2934</v>
+        <v>2933</v>
       </c>
       <c r="P27" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="Q27" s="51">
         <v>0.86</v>
       </c>
       <c r="R27" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="S27" s="54" cm="1">
         <f t="array" ref="S27">1-SUM(IF(ISNUMBER(P27:Q27), P27:Q27, 0))</f>
@@ -42688,13 +42706,13 @@
       <c r="T27" s="52"/>
       <c r="U27" s="56"/>
       <c r="V27" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="W27" s="51">
         <v>0.86</v>
       </c>
       <c r="X27" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="Y27" s="54" cm="1">
         <f t="array" ref="Y27">1-SUM(IF(ISNUMBER(V27:W27), V27:W27, 0))</f>
@@ -42715,7 +42733,7 @@
         <v>43</v>
       </c>
       <c r="C28" s="57" t="s">
-        <v>2815</v>
+        <v>2814</v>
       </c>
       <c r="D28" t="s">
         <v>44</v>
@@ -42742,29 +42760,29 @@
         <v>2642</v>
       </c>
       <c r="K28" s="67" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="L28" s="67">
         <v>106.16</v>
       </c>
       <c r="M28" s="68" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="N28" s="62">
         <f>M28*'Split Polyamides &amp; Isocyanates'!$C$37/L28</f>
         <v>0.90512434061793512</v>
       </c>
       <c r="O28" s="69" t="s">
-        <v>2970</v>
+        <v>2969</v>
       </c>
       <c r="P28" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="Q28" s="51">
         <v>0.48</v>
       </c>
       <c r="R28" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="S28" s="54" cm="1">
         <f t="array" ref="S28">1-SUM(IF(ISNUMBER(P28:Q28), P28:Q28, 0))</f>
@@ -42773,13 +42791,13 @@
       <c r="T28" s="52"/>
       <c r="U28" s="56"/>
       <c r="V28" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="W28" s="51">
         <v>0.48</v>
       </c>
       <c r="X28" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="Y28" s="54" cm="1">
         <f t="array" ref="Y28">1-SUM(IF(ISNUMBER(V28:W28), V28:W28, 0))</f>
@@ -42800,7 +42818,7 @@
         <v>37</v>
       </c>
       <c r="C29" s="57" t="s">
-        <v>2816</v>
+        <v>2815</v>
       </c>
       <c r="D29" t="s">
         <v>38</v>
@@ -42827,23 +42845,23 @@
         <v>2642</v>
       </c>
       <c r="K29" s="67" t="s">
-        <v>2935</v>
+        <v>2934</v>
       </c>
       <c r="L29" s="67">
         <v>92.14</v>
       </c>
       <c r="M29" s="68" t="s">
-        <v>2936</v>
+        <v>2935</v>
       </c>
       <c r="N29" s="62">
         <f>M29*'Split Polyamides &amp; Isocyanates'!$C$37/L29</f>
         <v>0.91249186021271977</v>
       </c>
       <c r="O29" s="69" t="s">
-        <v>2937</v>
+        <v>2936</v>
       </c>
       <c r="P29" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="Q29" s="51">
         <v>1</v>
@@ -42853,7 +42871,7 @@
       <c r="T29" s="52"/>
       <c r="U29" s="56"/>
       <c r="V29" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="W29" s="51">
         <v>1</v>
@@ -42875,7 +42893,7 @@
         <v>420</v>
       </c>
       <c r="C30" s="57" t="s">
-        <v>2817</v>
+        <v>2816</v>
       </c>
       <c r="D30" t="s">
         <v>421</v>
@@ -42902,29 +42920,29 @@
         <v>2642</v>
       </c>
       <c r="K30" s="67" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
       <c r="L30" s="67">
         <v>58.08</v>
       </c>
       <c r="M30" s="68" t="s">
-        <v>2881</v>
+        <v>2880</v>
       </c>
       <c r="N30" s="62">
         <f>M30*'Split Polyamides &amp; Isocyanates'!$C$37/L30</f>
         <v>0.62040289256198355</v>
       </c>
       <c r="O30" s="69" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="P30" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="Q30" s="51">
         <v>0.93</v>
       </c>
       <c r="R30" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="S30" s="54" cm="1">
         <f t="array" ref="S30">1-SUM(IF(ISNUMBER(P30:Q30), P30:Q30, 0))</f>
@@ -42933,13 +42951,13 @@
       <c r="T30" s="52"/>
       <c r="U30" s="56"/>
       <c r="V30" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="W30" s="51">
         <v>0.93</v>
       </c>
       <c r="X30" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="Y30" s="54" cm="1">
         <f t="array" ref="Y30">1-SUM(IF(ISNUMBER(V30:W30), V30:W30, 0))</f>
@@ -42960,13 +42978,13 @@
         <v>387</v>
       </c>
       <c r="C31" s="57" t="s">
-        <v>2819</v>
+        <v>2818</v>
       </c>
       <c r="D31" t="s">
         <v>388</v>
       </c>
       <c r="E31" s="41" t="s">
-        <v>2941</v>
+        <v>2940</v>
       </c>
       <c r="F31" s="49">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B31, prodcom_data[product], 0))</f>
@@ -42987,29 +43005,29 @@
         <v>2642</v>
       </c>
       <c r="K31" s="67" t="s">
-        <v>2942</v>
+        <v>2941</v>
       </c>
       <c r="L31" s="67">
         <v>30.026</v>
       </c>
       <c r="M31" s="68" t="s">
-        <v>2894</v>
+        <v>2893</v>
       </c>
       <c r="N31" s="62">
         <f>M31*'Split Polyamides &amp; Isocyanates'!$C$37/L31</f>
         <v>0.40001998268167588</v>
       </c>
       <c r="O31" s="69" t="s">
-        <v>2943</v>
+        <v>2942</v>
       </c>
       <c r="P31" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="Q31" s="51">
         <v>0.99</v>
       </c>
       <c r="R31" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="S31" s="54" cm="1">
         <f t="array" ref="S31">1-SUM(IF(ISNUMBER(P31:Q31), P31:Q31, 0))</f>
@@ -43018,13 +43036,13 @@
       <c r="T31" s="52"/>
       <c r="U31" s="56"/>
       <c r="V31" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="W31" s="51">
         <v>0.99</v>
       </c>
       <c r="X31" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="Y31" s="54" cm="1">
         <f t="array" ref="Y31">1-SUM(IF(ISNUMBER(V31:W31), V31:W31, 0))</f>
@@ -43045,13 +43063,13 @@
         <v>620</v>
       </c>
       <c r="C32" s="57" t="s">
-        <v>2820</v>
+        <v>2819</v>
       </c>
       <c r="D32" t="s">
         <v>621</v>
       </c>
       <c r="E32" s="41" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="F32" s="49">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B32, prodcom_data[product], 0))</f>
@@ -43072,29 +43090,29 @@
         <v>2642</v>
       </c>
       <c r="K32" s="67" t="s">
-        <v>2929</v>
+        <v>2928</v>
       </c>
       <c r="L32" s="67">
         <v>86.09</v>
       </c>
       <c r="M32" s="68" t="s">
-        <v>2914</v>
+        <v>2913</v>
       </c>
       <c r="N32" s="62">
         <f>M32*'Split Polyamides &amp; Isocyanates'!$C$37/L32</f>
         <v>0.55806713904053895</v>
       </c>
       <c r="O32" s="69" t="s">
-        <v>2930</v>
+        <v>2929</v>
       </c>
       <c r="P32" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="Q32" s="51">
         <v>0.99</v>
       </c>
       <c r="R32" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="S32" s="54" cm="1">
         <f t="array" ref="S32">1-SUM(IF(ISNUMBER(P32:Q32), P32:Q32, 0))</f>
@@ -43103,13 +43121,13 @@
       <c r="T32" s="52"/>
       <c r="U32" s="56"/>
       <c r="V32" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="W32" s="51">
         <v>0.99</v>
       </c>
       <c r="X32" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="Y32" s="54" cm="1">
         <f t="array" ref="Y32">1-SUM(IF(ISNUMBER(V32:W32), V32:W32, 0))</f>
@@ -43130,7 +43148,7 @@
         <v>205</v>
       </c>
       <c r="C33" s="57" t="s">
-        <v>2821</v>
+        <v>2820</v>
       </c>
       <c r="D33" t="s">
         <v>206</v>
@@ -43157,23 +43175,23 @@
         <v>2642</v>
       </c>
       <c r="K33" s="67" t="s">
-        <v>2944</v>
+        <v>2943</v>
       </c>
       <c r="L33" s="67">
         <v>60.05</v>
       </c>
       <c r="M33" s="68" t="s">
-        <v>2887</v>
+        <v>2886</v>
       </c>
       <c r="N33" s="62">
         <f>M33*'Split Polyamides &amp; Isocyanates'!$C$37/L33</f>
         <v>0.40003330557868444</v>
       </c>
       <c r="O33" s="69" t="s">
-        <v>2945</v>
+        <v>2944</v>
       </c>
       <c r="P33" s="52" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="Q33" s="51">
         <v>1</v>
@@ -43183,7 +43201,7 @@
       <c r="T33" s="52"/>
       <c r="U33" s="56"/>
       <c r="V33" s="52" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="W33" s="51">
         <v>1</v>
@@ -43205,13 +43223,13 @@
         <v>473</v>
       </c>
       <c r="C34" s="57" t="s">
-        <v>2822</v>
+        <v>2821</v>
       </c>
       <c r="D34" t="s">
         <v>474</v>
       </c>
       <c r="E34" s="41" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
       <c r="F34" s="49">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B34, prodcom_data[product], 0))</f>
@@ -43232,23 +43250,23 @@
         <v>2642</v>
       </c>
       <c r="K34" s="67" t="s">
-        <v>2952</v>
+        <v>2951</v>
       </c>
       <c r="L34" s="67">
         <v>44.05</v>
       </c>
       <c r="M34" s="68" t="s">
-        <v>2887</v>
+        <v>2886</v>
       </c>
       <c r="N34" s="62">
         <f>M34*'Split Polyamides &amp; Isocyanates'!$C$37/L34</f>
         <v>0.54533484676503974</v>
       </c>
       <c r="O34" s="69" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="P34" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="Q34" s="51">
         <v>1</v>
@@ -43258,7 +43276,7 @@
       <c r="T34" s="52"/>
       <c r="U34" s="56"/>
       <c r="V34" s="52" t="s">
-        <v>3033</v>
+        <v>3032</v>
       </c>
       <c r="W34" s="51">
         <v>1</v>
@@ -43280,13 +43298,13 @@
         <v>78</v>
       </c>
       <c r="C35" s="57" t="s">
-        <v>2823</v>
+        <v>2822</v>
       </c>
       <c r="D35" t="s">
         <v>79</v>
       </c>
       <c r="E35" s="41" t="s">
-        <v>2950</v>
+        <v>2949</v>
       </c>
       <c r="F35" s="49">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B35, prodcom_data[product], 0))</f>
@@ -43307,29 +43325,29 @@
         <v>2642</v>
       </c>
       <c r="K35" s="67" t="s">
-        <v>2900</v>
+        <v>2899</v>
       </c>
       <c r="L35" s="67">
         <v>62.5</v>
       </c>
       <c r="M35" s="68" t="s">
-        <v>2887</v>
+        <v>2886</v>
       </c>
       <c r="N35" s="62">
         <f>M35*'Split Polyamides &amp; Isocyanates'!$C$37/L35</f>
         <v>0.38435199999999997</v>
       </c>
       <c r="O35" s="69" t="s">
-        <v>2901</v>
+        <v>2900</v>
       </c>
       <c r="P35" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="Q35" s="51">
         <v>0.98</v>
       </c>
       <c r="R35" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="S35" s="54" cm="1">
         <f t="array" ref="S35">1-SUM(IF(ISNUMBER(P35:Q35), P35:Q35, 0))</f>
@@ -43338,19 +43356,19 @@
       <c r="T35" s="52"/>
       <c r="U35" s="56"/>
       <c r="V35" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="W35" s="51">
         <v>0.98</v>
       </c>
       <c r="X35" s="52" t="s">
-        <v>3084</v>
+        <v>3078</v>
       </c>
       <c r="Y35" s="53">
         <v>0.01</v>
       </c>
       <c r="Z35" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="AA35" s="54" cm="1">
         <f t="array" ref="AA35">1-SUM(IF(ISNUMBER(V35:Y35), V35:Y35, 0))</f>
@@ -43369,13 +43387,13 @@
         <v>293</v>
       </c>
       <c r="C36" s="57" t="s">
-        <v>2824</v>
+        <v>2823</v>
       </c>
       <c r="D36" t="s">
         <v>294</v>
       </c>
       <c r="E36" s="41" t="s">
-        <v>2938</v>
+        <v>2937</v>
       </c>
       <c r="F36" s="49">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B36, prodcom_data[product], 0))</f>
@@ -43396,29 +43414,29 @@
         <v>2642</v>
       </c>
       <c r="K36" s="67" t="s">
-        <v>2939</v>
+        <v>2938</v>
       </c>
       <c r="L36" s="67">
         <v>93.13</v>
       </c>
       <c r="M36" s="68" t="s">
-        <v>2897</v>
+        <v>2896</v>
       </c>
       <c r="N36" s="62">
         <f>M36*'Split Polyamides &amp; Isocyanates'!$C$37/L36</f>
         <v>0.77382153978309898</v>
       </c>
       <c r="O36" s="69" t="s">
-        <v>2940</v>
+        <v>2939</v>
       </c>
       <c r="P36" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="Q36" s="51">
         <v>0.8</v>
       </c>
       <c r="R36" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="S36" s="54" cm="1">
         <f t="array" ref="S36">1-SUM(IF(ISNUMBER(P36:Q36), P36:Q36, 0))</f>
@@ -43427,13 +43445,13 @@
       <c r="T36" s="52"/>
       <c r="U36" s="56"/>
       <c r="V36" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="W36" s="51">
         <v>0.8</v>
       </c>
       <c r="X36" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="Y36" s="54" cm="1">
         <f t="array" ref="Y36">1-SUM(IF(ISNUMBER(V36:W36), V36:W36, 0))</f>
@@ -43454,13 +43472,13 @@
         <v>602</v>
       </c>
       <c r="C37" s="57" t="s">
-        <v>2825</v>
+        <v>2824</v>
       </c>
       <c r="D37" t="s">
         <v>603</v>
       </c>
       <c r="E37" s="41" t="s">
-        <v>2906</v>
+        <v>2905</v>
       </c>
       <c r="F37" s="49">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B37, prodcom_data[product], 0))</f>
@@ -43481,23 +43499,23 @@
         <v>2642</v>
       </c>
       <c r="K37" s="67" t="s">
-        <v>2907</v>
+        <v>2906</v>
       </c>
       <c r="L37" s="67">
         <v>222.24</v>
       </c>
       <c r="M37" s="68" t="s">
-        <v>2908</v>
+        <v>2907</v>
       </c>
       <c r="N37" s="62">
         <f>M37*'Split Polyamides &amp; Isocyanates'!$C$37/L37</f>
         <v>0.64854211663066952</v>
       </c>
       <c r="O37" s="69" t="s">
-        <v>2909</v>
+        <v>2908</v>
       </c>
       <c r="P37" s="52" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="Q37" s="51">
         <v>1</v>
@@ -43507,7 +43525,7 @@
       <c r="T37" s="52"/>
       <c r="U37" s="56"/>
       <c r="V37" s="52" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="W37" s="51">
         <v>1</v>
@@ -43529,13 +43547,13 @@
         <v>135</v>
       </c>
       <c r="C38" s="57" t="s">
-        <v>2826</v>
+        <v>2825</v>
       </c>
       <c r="D38" t="s">
         <v>136</v>
       </c>
       <c r="E38" s="41" t="s">
-        <v>2972</v>
+        <v>2971</v>
       </c>
       <c r="F38" s="49">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B38, prodcom_data[product], 0))</f>
@@ -43556,29 +43574,29 @@
         <v>2642</v>
       </c>
       <c r="K38" s="67" t="s">
-        <v>2973</v>
+        <v>2972</v>
       </c>
       <c r="L38" s="67">
         <v>76.09</v>
       </c>
       <c r="M38" s="68" t="s">
-        <v>2881</v>
+        <v>2880</v>
       </c>
       <c r="N38" s="62">
         <f>M38*'Split Polyamides &amp; Isocyanates'!$C$37/L38</f>
         <v>0.47355762912340649</v>
       </c>
       <c r="O38" s="69" t="s">
-        <v>2974</v>
+        <v>2973</v>
       </c>
       <c r="P38" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="Q38" s="51">
         <v>0.95</v>
       </c>
       <c r="R38" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="S38" s="54" cm="1">
         <f t="array" ref="S38">1-SUM(IF(ISNUMBER(P38:Q38), P38:Q38, 0))</f>
@@ -43587,13 +43605,13 @@
       <c r="T38" s="52"/>
       <c r="U38" s="56"/>
       <c r="V38" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="W38" s="51">
         <v>0.95</v>
       </c>
       <c r="X38" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="Y38" s="54" cm="1">
         <f t="array" ref="Y38">1-SUM(IF(ISNUMBER(V38:W38), V38:W38, 0))</f>
@@ -43614,13 +43632,13 @@
         <v>557</v>
       </c>
       <c r="C39" s="57" t="s">
-        <v>2827</v>
+        <v>2826</v>
       </c>
       <c r="D39" t="s">
         <v>558</v>
       </c>
       <c r="E39" s="41" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="F39" s="49">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B39, prodcom_data[product], 0))</f>
@@ -43641,23 +43659,23 @@
         <v>2642</v>
       </c>
       <c r="K39" s="67" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="L39" s="67">
         <v>211.3</v>
       </c>
       <c r="M39" s="68" t="s">
-        <v>2948</v>
+        <v>2947</v>
       </c>
       <c r="N39" s="62">
         <f>M39*'Split Polyamides &amp; Isocyanates'!$C$37/L39</f>
         <v>0.85265026029342161</v>
       </c>
       <c r="O39" s="69" t="s">
-        <v>2949</v>
+        <v>2948</v>
       </c>
       <c r="P39" s="52" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="Q39" s="51">
         <v>1</v>
@@ -43667,7 +43685,7 @@
       <c r="T39" s="52"/>
       <c r="U39" s="56"/>
       <c r="V39" s="52" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="W39" s="51">
         <v>1</v>
@@ -43689,13 +43707,13 @@
         <v>46</v>
       </c>
       <c r="C40" s="57" t="s">
-        <v>2828</v>
+        <v>2827</v>
       </c>
       <c r="D40" t="s">
         <v>47</v>
       </c>
       <c r="E40" s="41" t="s">
-        <v>2981</v>
+        <v>2980</v>
       </c>
       <c r="F40" s="49">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B40, prodcom_data[product], 0))</f>
@@ -43716,29 +43734,29 @@
         <v>2642</v>
       </c>
       <c r="K40" s="67" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="L40" s="67">
         <v>106.16</v>
       </c>
       <c r="M40" s="68" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="N40" s="62">
         <f>M40*'Split Polyamides &amp; Isocyanates'!$C$37/L40</f>
         <v>0.90512434061793512</v>
       </c>
       <c r="O40" s="69" t="s">
-        <v>2982</v>
+        <v>2981</v>
       </c>
       <c r="P40" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="Q40" s="51">
         <v>0.97</v>
       </c>
       <c r="R40" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="S40" s="54" cm="1">
         <f t="array" ref="S40">1-SUM(IF(ISNUMBER(P40:Q40), P40:Q40, 0))</f>
@@ -43747,13 +43765,13 @@
       <c r="T40" s="52"/>
       <c r="U40" s="56"/>
       <c r="V40" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="W40" s="51">
         <v>0.97</v>
       </c>
       <c r="X40" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="Y40" s="54" cm="1">
         <f t="array" ref="Y40">1-SUM(IF(ISNUMBER(V40:W40), V40:W40, 0))</f>
@@ -43774,13 +43792,13 @@
         <v>569</v>
       </c>
       <c r="C41" s="57" t="s">
-        <v>2829</v>
+        <v>2828</v>
       </c>
       <c r="D41" t="s">
         <v>570</v>
       </c>
       <c r="E41" s="41" t="s">
-        <v>2899</v>
+        <v>2898</v>
       </c>
       <c r="F41" s="49">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B41, prodcom_data[product], 0))</f>
@@ -43801,29 +43819,29 @@
         <v>2642</v>
       </c>
       <c r="K41" s="67" t="s">
-        <v>2900</v>
+        <v>2899</v>
       </c>
       <c r="L41" s="67">
         <v>62.5</v>
       </c>
       <c r="M41" s="68" t="s">
-        <v>2887</v>
+        <v>2886</v>
       </c>
       <c r="N41" s="62">
         <f>M41*'Split Polyamides &amp; Isocyanates'!$C$37/L41</f>
         <v>0.38435199999999997</v>
       </c>
       <c r="O41" s="69" t="s">
-        <v>2901</v>
+        <v>2900</v>
       </c>
       <c r="P41" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="Q41" s="51">
         <v>0.98</v>
       </c>
       <c r="R41" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="S41" s="54" cm="1">
         <f t="array" ref="S41">1-SUM(IF(ISNUMBER(P41:Q41), P41:Q41, 0))</f>
@@ -43832,13 +43850,13 @@
       <c r="T41" s="52"/>
       <c r="U41" s="56"/>
       <c r="V41" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="W41" s="51">
         <v>0.98</v>
       </c>
       <c r="X41" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="Y41" s="54" cm="1">
         <f t="array" ref="Y41">1-SUM(IF(ISNUMBER(V41:W41), V41:W41, 0))</f>
@@ -43859,7 +43877,7 @@
         <v>55</v>
       </c>
       <c r="C42" s="57" t="s">
-        <v>2830</v>
+        <v>2829</v>
       </c>
       <c r="D42" t="s">
         <v>56</v>
@@ -43886,29 +43904,29 @@
         <v>2642</v>
       </c>
       <c r="K42" s="67" t="s">
-        <v>2962</v>
+        <v>2961</v>
       </c>
       <c r="L42" s="67">
         <v>120.19</v>
       </c>
       <c r="M42" s="68" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="N42" s="62">
         <f>M42*'Split Polyamides &amp; Isocyanates'!$C$37/L42</f>
         <v>0.89940094849821106</v>
       </c>
       <c r="O42" s="69" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="P42" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="Q42" s="51">
         <v>0.94</v>
       </c>
       <c r="R42" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="S42" s="54" cm="1">
         <f t="array" ref="S42">1-SUM(IF(ISNUMBER(P42:Q42), P42:Q42, 0))</f>
@@ -43917,13 +43935,13 @@
       <c r="T42" s="52"/>
       <c r="U42" s="56"/>
       <c r="V42" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="W42" s="51">
         <v>0.94</v>
       </c>
       <c r="X42" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="Y42" s="54" cm="1">
         <f t="array" ref="Y42">1-SUM(IF(ISNUMBER(V42:W42), V42:W42, 0))</f>
@@ -43944,7 +43962,7 @@
         <v>332</v>
       </c>
       <c r="C43" s="57" t="s">
-        <v>2831</v>
+        <v>2830</v>
       </c>
       <c r="D43" t="s">
         <v>333</v>
@@ -43971,23 +43989,23 @@
         <v>2642</v>
       </c>
       <c r="K43" s="67" t="s">
-        <v>2987</v>
+        <v>2986</v>
       </c>
       <c r="L43" s="67">
         <v>53.06</v>
       </c>
       <c r="M43" s="68" t="s">
-        <v>2881</v>
+        <v>2880</v>
       </c>
       <c r="N43" s="62">
         <f>M43*'Split Polyamides &amp; Isocyanates'!$C$37/L43</f>
         <v>0.67909913305691672</v>
       </c>
       <c r="O43" s="69" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="P43" s="52" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="Q43" s="51">
         <v>1</v>
@@ -43997,7 +44015,7 @@
       <c r="T43" s="52"/>
       <c r="U43" s="56"/>
       <c r="V43" s="52" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="W43" s="51">
         <v>1</v>
@@ -44019,7 +44037,7 @@
         <v>28</v>
       </c>
       <c r="C44" s="57" t="s">
-        <v>2832</v>
+        <v>2831</v>
       </c>
       <c r="D44" t="s">
         <v>29</v>
@@ -44046,23 +44064,23 @@
         <v>2642</v>
       </c>
       <c r="K44" s="67" t="s">
-        <v>2965</v>
+        <v>2964</v>
       </c>
       <c r="L44" s="67">
         <v>84.16</v>
       </c>
       <c r="M44" s="68" t="s">
-        <v>2897</v>
+        <v>2896</v>
       </c>
       <c r="N44" s="62">
         <f>M44*'Split Polyamides &amp; Isocyanates'!$C$37/L44</f>
         <v>0.85629752851711038</v>
       </c>
       <c r="O44" s="69" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="P44" s="52" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="Q44" s="51">
         <v>1</v>
@@ -44072,7 +44090,7 @@
       <c r="T44" s="52"/>
       <c r="U44" s="56"/>
       <c r="V44" s="52" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="W44" s="51">
         <v>1</v>
@@ -44094,13 +44112,13 @@
         <v>252</v>
       </c>
       <c r="C45" s="57" t="s">
-        <v>2833</v>
+        <v>2832</v>
       </c>
       <c r="D45" t="s">
         <v>253</v>
       </c>
       <c r="E45" s="41" t="s">
-        <v>2856</v>
+        <v>2855</v>
       </c>
       <c r="F45" s="49">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B45, prodcom_data[product], 0))</f>
@@ -44121,23 +44139,23 @@
         <v>2642</v>
       </c>
       <c r="K45" s="67" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="L45" s="67">
         <v>146.13999999999999</v>
       </c>
       <c r="M45" s="68" t="s">
-        <v>2897</v>
+        <v>2896</v>
       </c>
       <c r="N45" s="62">
         <f>M45*'Split Polyamides &amp; Isocyanates'!$C$37/L45</f>
         <v>0.49312987546188591</v>
       </c>
       <c r="O45" s="69" t="s">
-        <v>2968</v>
+        <v>2967</v>
       </c>
       <c r="P45" s="52" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="Q45" s="51">
         <v>1</v>
@@ -44147,7 +44165,7 @@
       <c r="T45" s="52"/>
       <c r="U45" s="56"/>
       <c r="V45" s="52" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="W45" s="51">
         <v>1</v>
@@ -44169,13 +44187,13 @@
         <v>114</v>
       </c>
       <c r="C46" s="57" t="s">
-        <v>2834</v>
+        <v>2833</v>
       </c>
       <c r="D46" t="s">
         <v>115</v>
       </c>
       <c r="E46" s="41" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="F46" s="49">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B46, prodcom_data[product], 0))</f>
@@ -44196,29 +44214,29 @@
         <v>2687</v>
       </c>
       <c r="K46" s="67" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="L46" s="67">
         <v>60.1</v>
       </c>
       <c r="M46" s="68" t="s">
-        <v>2881</v>
+        <v>2880</v>
       </c>
       <c r="N46" s="62">
         <f>M46*'Split Polyamides &amp; Isocyanates'!$C$37/L46</f>
         <v>0.59955074875207992</v>
       </c>
       <c r="O46" s="69" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="P46" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="Q46" s="51">
         <v>0.82</v>
       </c>
       <c r="R46" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="S46" s="54" cm="1">
         <f t="array" ref="S46">1-SUM(IF(ISNUMBER(P46:Q46), P46:Q46, 0))</f>
@@ -44227,13 +44245,13 @@
       <c r="T46" s="52"/>
       <c r="U46" s="56"/>
       <c r="V46" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="W46" s="51">
         <v>0.82</v>
       </c>
       <c r="X46" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="Y46" s="54" cm="1">
         <f t="array" ref="Y46">1-SUM(IF(ISNUMBER(V46:W46), V46:W46, 0))</f>
@@ -44254,7 +44272,7 @@
         <v>52</v>
       </c>
       <c r="C47" s="57" t="s">
-        <v>2835</v>
+        <v>2834</v>
       </c>
       <c r="D47" t="s">
         <v>53</v>
@@ -44281,29 +44299,29 @@
         <v>2642</v>
       </c>
       <c r="K47" s="67" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="L47" s="67">
         <v>106.16</v>
       </c>
       <c r="M47" s="68" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="N47" s="62">
         <f>M47*'Split Polyamides &amp; Isocyanates'!$C$37/L47</f>
         <v>0.90512434061793512</v>
       </c>
       <c r="O47" s="69" t="s">
-        <v>2971</v>
+        <v>2970</v>
       </c>
       <c r="P47" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="Q47" s="51">
         <v>0.99</v>
       </c>
       <c r="R47" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="S47" s="54" cm="1">
         <f t="array" ref="S47">1-SUM(IF(ISNUMBER(P47:Q47), P47:Q47, 0))</f>
@@ -44312,13 +44330,13 @@
       <c r="T47" s="52"/>
       <c r="U47" s="56"/>
       <c r="V47" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="W47" s="51">
         <v>0.99</v>
       </c>
       <c r="X47" s="52" t="s">
-        <v>3035</v>
+        <v>3034</v>
       </c>
       <c r="Y47" s="53">
         <v>0.01</v>
@@ -44338,7 +44356,7 @@
         <v>220</v>
       </c>
       <c r="C48" s="57" t="s">
-        <v>2836</v>
+        <v>2835</v>
       </c>
       <c r="D48" t="s">
         <v>221</v>
@@ -44365,29 +44383,29 @@
         <v>2689</v>
       </c>
       <c r="K48" s="67" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="L48" s="67">
         <v>128.16900000000001</v>
       </c>
       <c r="M48" s="68" t="s">
-        <v>2936</v>
+        <v>2935</v>
       </c>
       <c r="N48" s="62">
         <f>M48*'Split Polyamides &amp; Isocyanates'!$C$37/L48</f>
         <v>0.6559854567016985</v>
       </c>
       <c r="O48" s="69" t="s">
-        <v>2958</v>
+        <v>2957</v>
       </c>
       <c r="P48" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="Q48" s="51">
         <v>0.72</v>
       </c>
       <c r="R48" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="S48" s="54" cm="1">
         <f t="array" ref="S48">1-SUM(IF(ISNUMBER(P48:Q48), P48:Q48, 0))</f>
@@ -44396,13 +44414,13 @@
       <c r="T48" s="52"/>
       <c r="U48" s="56"/>
       <c r="V48" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="W48" s="51">
         <v>0.72</v>
       </c>
       <c r="X48" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="Y48" s="54" cm="1">
         <f t="array" ref="Y48">1-SUM(IF(ISNUMBER(V48:W48), V48:W48, 0))</f>
@@ -44423,13 +44441,13 @@
         <v>542</v>
       </c>
       <c r="C49" s="57" t="s">
-        <v>2837</v>
+        <v>2836</v>
       </c>
       <c r="D49" t="s">
         <v>543</v>
       </c>
       <c r="E49" s="41" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="F49" s="49">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B49, prodcom_data[product], 0))</f>
@@ -44450,29 +44468,29 @@
         <v>2642</v>
       </c>
       <c r="K49" s="67" t="s">
-        <v>2955</v>
+        <v>2954</v>
       </c>
       <c r="L49" s="67">
         <v>114.14</v>
       </c>
       <c r="M49" s="68" t="s">
-        <v>2897</v>
+        <v>2896</v>
       </c>
       <c r="N49" s="62">
         <f>M49*'Split Polyamides &amp; Isocyanates'!$C$37/L49</f>
         <v>0.63138251270369727</v>
       </c>
       <c r="O49" s="69" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="P49" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="Q49" s="51">
         <v>0.87</v>
       </c>
       <c r="R49" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="S49" s="54" cm="1">
         <f t="array" ref="S49">1-SUM(IF(ISNUMBER(P49:Q49), P49:Q49, 0))</f>
@@ -44481,13 +44499,13 @@
       <c r="T49" s="52"/>
       <c r="U49" s="56"/>
       <c r="V49" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="W49" s="51">
         <v>0.87</v>
       </c>
       <c r="X49" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="Y49" s="54" cm="1">
         <f t="array" ref="Y49">1-SUM(IF(ISNUMBER(V49:W49), V49:W49, 0))</f>
@@ -44508,13 +44526,13 @@
         <v>117</v>
       </c>
       <c r="C50" s="57" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
       <c r="D50" t="s">
         <v>118</v>
       </c>
       <c r="E50" s="41" t="s">
-        <v>2975</v>
+        <v>2974</v>
       </c>
       <c r="F50" s="49">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B50, prodcom_data[product], 0))</f>
@@ -44535,23 +44553,23 @@
         <v>2642</v>
       </c>
       <c r="K50" s="67" t="s">
-        <v>2976</v>
+        <v>2975</v>
       </c>
       <c r="L50" s="67">
         <v>74.12</v>
       </c>
       <c r="M50" s="68" t="s">
-        <v>2914</v>
+        <v>2913</v>
       </c>
       <c r="N50" s="62">
         <f>M50*'Split Polyamides &amp; Isocyanates'!$C$37/L50</f>
         <v>0.64819212088505118</v>
       </c>
       <c r="O50" s="69" t="s">
-        <v>2977</v>
+        <v>2976</v>
       </c>
       <c r="P50" s="52" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="Q50" s="51">
         <v>1</v>
@@ -44561,7 +44579,7 @@
       <c r="T50" s="52"/>
       <c r="U50" s="56"/>
       <c r="V50" s="52" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="W50" s="51">
         <v>1</v>
@@ -44583,13 +44601,13 @@
         <v>284</v>
       </c>
       <c r="C51" s="57" t="s">
-        <v>2839</v>
+        <v>2838</v>
       </c>
       <c r="D51" t="s">
         <v>285</v>
       </c>
       <c r="E51" s="41" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="F51" s="49">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B51, prodcom_data[product], 0))</f>
@@ -44610,29 +44628,29 @@
         <v>2693</v>
       </c>
       <c r="K51" s="67" t="s">
-        <v>2979</v>
+        <v>2978</v>
       </c>
       <c r="L51" s="67">
         <v>116.2</v>
       </c>
       <c r="M51" s="68" t="s">
-        <v>2897</v>
+        <v>2896</v>
       </c>
       <c r="N51" s="62">
         <f>M51*'Split Polyamides &amp; Isocyanates'!$C$37/L51</f>
         <v>0.6201893287435456</v>
       </c>
       <c r="O51" s="69" t="s">
-        <v>2980</v>
+        <v>2979</v>
       </c>
       <c r="P51" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="Q51" s="51">
         <v>0.91</v>
       </c>
       <c r="R51" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="S51" s="54" cm="1">
         <f t="array" ref="S51">1-SUM(IF(ISNUMBER(P51:Q51), P51:Q51, 0))</f>
@@ -44641,13 +44659,13 @@
       <c r="T51" s="52"/>
       <c r="U51" s="56"/>
       <c r="V51" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="W51" s="51">
         <v>0.91</v>
       </c>
       <c r="X51" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="Y51" s="54" cm="1">
         <f t="array" ref="Y51">1-SUM(IF(ISNUMBER(V51:W51), V51:W51, 0))</f>
@@ -44668,7 +44686,7 @@
         <v>186</v>
       </c>
       <c r="C52" s="57" t="s">
-        <v>2840</v>
+        <v>2839</v>
       </c>
       <c r="D52" t="s">
         <v>187</v>
@@ -44695,23 +44713,23 @@
         <v>2642</v>
       </c>
       <c r="K52" s="67" t="s">
-        <v>2993</v>
+        <v>2992</v>
       </c>
       <c r="L52" s="67">
         <v>88.11</v>
       </c>
       <c r="M52" s="68" t="s">
-        <v>2914</v>
+        <v>2913</v>
       </c>
       <c r="N52" s="62">
         <f>M52*'Split Polyamides &amp; Isocyanates'!$C$37/L52</f>
         <v>0.54527295426171829</v>
       </c>
       <c r="O52" s="69" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="P52" s="52" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="Q52" s="51">
         <v>1</v>
@@ -44721,7 +44739,7 @@
       <c r="T52" s="52"/>
       <c r="U52" s="56"/>
       <c r="V52" s="52" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="W52" s="51">
         <v>1</v>
@@ -44743,13 +44761,13 @@
         <v>581</v>
       </c>
       <c r="C53" s="57" t="s">
-        <v>2841</v>
+        <v>2840</v>
       </c>
       <c r="D53" t="s">
         <v>582</v>
       </c>
       <c r="E53" s="41" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="F53" s="49">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B53, prodcom_data[product], 0))</f>
@@ -44764,26 +44782,26 @@
         <v>0.59226283959165005</v>
       </c>
       <c r="I53" s="44" t="s">
-        <v>2990</v>
+        <v>2989</v>
       </c>
       <c r="J53" s="42" t="s">
         <v>2695</v>
       </c>
       <c r="K53" s="67" t="s">
-        <v>2991</v>
+        <v>2990</v>
       </c>
       <c r="L53" s="67">
         <v>30.026</v>
       </c>
       <c r="M53" s="68" t="s">
-        <v>2894</v>
+        <v>2893</v>
       </c>
       <c r="N53" s="62">
         <f>M53*'Split Polyamides &amp; Isocyanates'!$C$37/L53</f>
         <v>0.40001998268167588</v>
       </c>
       <c r="O53" s="69" t="s">
-        <v>2992</v>
+        <v>2991</v>
       </c>
       <c r="P53" s="52"/>
       <c r="Q53" s="53"/>
@@ -44810,13 +44828,13 @@
         <v>459</v>
       </c>
       <c r="C54" s="57" t="s">
-        <v>2842</v>
+        <v>2841</v>
       </c>
       <c r="D54" t="s">
         <v>460</v>
       </c>
       <c r="E54" s="41" t="s">
-        <v>2995</v>
+        <v>2994</v>
       </c>
       <c r="F54" s="49">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B54, prodcom_data[product], 0))</f>
@@ -44837,29 +44855,29 @@
         <v>2642</v>
       </c>
       <c r="K54" s="67" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="L54" s="67">
         <v>106.12</v>
       </c>
       <c r="M54" s="68" t="s">
-        <v>2914</v>
+        <v>2913</v>
       </c>
       <c r="N54" s="62">
         <f>M54*'Split Polyamides &amp; Isocyanates'!$C$37/L54</f>
         <v>0.45273275537127777</v>
       </c>
       <c r="O54" s="69" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
       <c r="P54" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="Q54" s="51">
         <v>0.21</v>
       </c>
       <c r="R54" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="S54" s="54" cm="1">
         <f t="array" ref="S54">1-SUM(IF(ISNUMBER(P54:Q54), P54:Q54, 0))</f>
@@ -44868,13 +44886,13 @@
       <c r="T54" s="52"/>
       <c r="U54" s="56"/>
       <c r="V54" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="W54" s="51">
         <v>0.21</v>
       </c>
       <c r="X54" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="Y54" s="54" cm="1">
         <f t="array" ref="Y54">1-SUM(IF(ISNUMBER(V54:W54), V54:W54, 0))</f>
@@ -44895,13 +44913,13 @@
         <v>226</v>
       </c>
       <c r="C55" s="57" t="s">
-        <v>2843</v>
+        <v>2842</v>
       </c>
       <c r="D55" t="s">
         <v>227</v>
       </c>
       <c r="E55" s="41" t="s">
-        <v>2983</v>
+        <v>2982</v>
       </c>
       <c r="F55" s="49">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B55, prodcom_data[product], 0))</f>
@@ -44922,29 +44940,29 @@
         <v>2698</v>
       </c>
       <c r="K55" s="67" t="s">
-        <v>2984</v>
+        <v>2983</v>
       </c>
       <c r="L55" s="67">
         <v>100.12</v>
       </c>
       <c r="M55" s="68" t="s">
-        <v>2985</v>
+        <v>2984</v>
       </c>
       <c r="N55" s="62">
         <f>M55*'Split Polyamides &amp; Isocyanates'!$C$37/L55</f>
         <v>0.59983020375549334</v>
       </c>
       <c r="O55" s="69" t="s">
-        <v>2986</v>
+        <v>2985</v>
       </c>
       <c r="P55" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="Q55" s="51">
         <v>0.35</v>
       </c>
       <c r="R55" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="S55" s="54" cm="1">
         <f t="array" ref="S55">1-SUM(IF(ISNUMBER(P55:Q55), P55:Q55, 0))</f>
@@ -44953,13 +44971,13 @@
       <c r="T55" s="52"/>
       <c r="U55" s="56"/>
       <c r="V55" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="W55" s="51">
         <v>0.35</v>
       </c>
       <c r="X55" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="Y55" s="54" cm="1">
         <f t="array" ref="Y55">1-SUM(IF(ISNUMBER(V55:W55), V55:W55, 0))</f>
@@ -44980,7 +44998,7 @@
         <v>40</v>
       </c>
       <c r="C56" s="57" t="s">
-        <v>2844</v>
+        <v>2843</v>
       </c>
       <c r="D56" t="s">
         <v>41</v>
@@ -45007,29 +45025,29 @@
         <v>2642</v>
       </c>
       <c r="K56" s="67" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="L56" s="67">
         <v>106.16</v>
       </c>
       <c r="M56" s="68" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="N56" s="62">
         <f>M56*'Split Polyamides &amp; Isocyanates'!$C$37/L56</f>
         <v>0.90512434061793512</v>
       </c>
       <c r="O56" s="69" t="s">
-        <v>2998</v>
+        <v>2997</v>
       </c>
       <c r="P56" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="Q56" s="51">
         <v>0.51</v>
       </c>
       <c r="R56" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="S56" s="54" cm="1">
         <f t="array" ref="S56">1-SUM(IF(ISNUMBER(P56:Q56), P56:Q56, 0))</f>
@@ -45038,13 +45056,13 @@
       <c r="T56" s="52"/>
       <c r="U56" s="56"/>
       <c r="V56" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="W56" s="51">
         <v>0.51</v>
       </c>
       <c r="X56" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="Y56" s="54" cm="1">
         <f t="array" ref="Y56">1-SUM(IF(ISNUMBER(V56:W56), V56:W56, 0))</f>
@@ -45071,7 +45089,7 @@
         <v>62</v>
       </c>
       <c r="E57" s="41" t="s">
-        <v>3069</v>
+        <v>3063</v>
       </c>
       <c r="F57" s="49">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B57, prodcom_data[product], 0))</f>
@@ -45086,13 +45104,13 @@
         <v>0.99702850277831634</v>
       </c>
       <c r="I57" s="42" t="s">
-        <v>3074</v>
+        <v>3068</v>
       </c>
       <c r="J57" s="42" t="s">
-        <v>3075</v>
+        <v>3069</v>
       </c>
       <c r="K57" s="67" t="s">
-        <v>3076</v>
+        <v>3070</v>
       </c>
       <c r="L57" s="67">
         <v>50.49</v>
@@ -45105,10 +45123,10 @@
         <v>0.23788869082986727</v>
       </c>
       <c r="O57" s="69" t="s">
-        <v>3077</v>
+        <v>3071</v>
       </c>
       <c r="P57" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="Q57" s="51">
         <v>1</v>
@@ -45118,7 +45136,7 @@
       <c r="T57" s="52"/>
       <c r="U57" s="56"/>
       <c r="V57" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="W57" s="51">
         <v>1</v>
@@ -45147,7 +45165,7 @@
         <v>394</v>
       </c>
       <c r="E58" s="41" t="s">
-        <v>3070</v>
+        <v>3064</v>
       </c>
       <c r="F58" s="49">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B58, prodcom_data[product], 0))</f>
@@ -45166,23 +45184,23 @@
       </c>
       <c r="J58" s="42"/>
       <c r="K58" s="67" t="s">
-        <v>3082</v>
+        <v>3076</v>
       </c>
       <c r="L58" s="67">
         <v>72.11</v>
       </c>
       <c r="M58" s="68" t="s">
-        <v>2914</v>
+        <v>2913</v>
       </c>
       <c r="N58" s="62">
         <f>M58*'Split Polyamides &amp; Isocyanates'!$C$37/L58</f>
         <v>0.66625988073776177</v>
       </c>
       <c r="O58" s="69" t="s">
-        <v>3083</v>
+        <v>3077</v>
       </c>
       <c r="P58" s="52" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="Q58" s="51">
         <v>1</v>
@@ -45192,7 +45210,7 @@
       <c r="T58" s="52"/>
       <c r="U58" s="56"/>
       <c r="V58" s="52" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="W58" s="51">
         <v>1</v>
@@ -45221,7 +45239,7 @@
         <v>165</v>
       </c>
       <c r="E59" s="41" t="s">
-        <v>3071</v>
+        <v>3065</v>
       </c>
       <c r="F59" s="49">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B59, prodcom_data[product], 0))</f>
@@ -45236,33 +45254,33 @@
         <v>0.77509698342872879</v>
       </c>
       <c r="I59" s="42" t="s">
-        <v>3072</v>
+        <v>3066</v>
       </c>
       <c r="J59" s="42"/>
       <c r="K59" s="67" t="s">
-        <v>3080</v>
+        <v>3074</v>
       </c>
       <c r="L59" s="67">
         <v>228.29</v>
       </c>
       <c r="M59" s="68" t="s">
-        <v>2948</v>
+        <v>2947</v>
       </c>
       <c r="N59" s="62">
         <f>M59*'Split Polyamides &amp; Isocyanates'!$C$37/L59</f>
         <v>0.78919356958254849</v>
       </c>
       <c r="O59" s="69" t="s">
-        <v>3081</v>
+        <v>3075</v>
       </c>
       <c r="P59" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="Q59" s="51">
         <v>0.78</v>
       </c>
       <c r="R59" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="S59" s="54" cm="1">
         <f t="array" ref="S59">1-SUM(IF(ISNUMBER(P59:Q59), P59:Q59, 0))</f>
@@ -45271,13 +45289,13 @@
       <c r="T59" s="52"/>
       <c r="U59" s="56"/>
       <c r="V59" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="W59" s="51">
         <v>0.78</v>
       </c>
       <c r="X59" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="Y59" s="54" cm="1">
         <f t="array" ref="Y59">1-SUM(IF(ISNUMBER(V59:W59), V59:W59, 0))</f>
@@ -45305,7 +45323,7 @@
         <v>624</v>
       </c>
       <c r="E60" s="41" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="F60" s="49">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B60, prodcom_data[product], 0))</f>
@@ -45324,29 +45342,29 @@
       </c>
       <c r="J60" s="42"/>
       <c r="K60" s="67" t="s">
-        <v>2929</v>
+        <v>2928</v>
       </c>
       <c r="L60" s="67">
         <v>86.08905</v>
       </c>
       <c r="M60" s="68" t="s">
-        <v>2914</v>
+        <v>2913</v>
       </c>
       <c r="N60" s="62">
         <f>M60*'Split Polyamides &amp; Isocyanates'!$C$37/L60</f>
         <v>0.55807329735895561</v>
       </c>
       <c r="O60" s="69" t="s">
-        <v>2930</v>
+        <v>2929</v>
       </c>
       <c r="P60" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="Q60" s="51">
         <v>0.87</v>
       </c>
       <c r="R60" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="S60" s="54" cm="1">
         <f t="array" ref="S60">1-SUM(IF(ISNUMBER(P60:Q60), P60:Q60, 0))</f>
@@ -45355,13 +45373,13 @@
       <c r="T60" s="52"/>
       <c r="U60" s="56"/>
       <c r="V60" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="W60" s="51">
         <v>0.87</v>
       </c>
       <c r="X60" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="Y60" s="54" cm="1">
         <f t="array" ref="Y60">1-SUM(IF(ISNUMBER(V60:W60), V60:W60, 0))</f>
@@ -45404,27 +45422,27 @@
         <v>1.1148601794389756E-2</v>
       </c>
       <c r="I61" s="42" t="s">
-        <v>3073</v>
+        <v>3067</v>
       </c>
       <c r="J61" s="42"/>
       <c r="K61" s="67" t="s">
-        <v>3078</v>
+        <v>3072</v>
       </c>
       <c r="L61" s="67">
         <v>102.09</v>
       </c>
       <c r="M61" s="68" t="s">
-        <v>2914</v>
+        <v>2913</v>
       </c>
       <c r="N61" s="62">
         <f>M61*'Split Polyamides &amp; Isocyanates'!$C$37/L61</f>
         <v>0.47060436869428929</v>
       </c>
       <c r="O61" s="69" t="s">
-        <v>3079</v>
+        <v>3073</v>
       </c>
       <c r="P61" s="52" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="Q61" s="51">
         <v>1</v>
@@ -45434,7 +45452,7 @@
       <c r="T61" s="52"/>
       <c r="U61" s="56"/>
       <c r="V61" s="52" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="W61" s="51">
         <v>1</v>
@@ -45457,13 +45475,13 @@
         <v>345</v>
       </c>
       <c r="C62" s="57" t="s">
-        <v>2818</v>
+        <v>2817</v>
       </c>
       <c r="D62" s="45" t="s">
+        <v>2998</v>
+      </c>
+      <c r="E62" s="41" t="s">
         <v>2999</v>
-      </c>
-      <c r="E62" s="41" t="s">
-        <v>3000</v>
       </c>
       <c r="F62" s="49">
         <f>'Split Polyamides &amp; Isocyanates'!C32*('Split Polyamides &amp; Isocyanates'!C29/SUM('Split Polyamides &amp; Isocyanates'!$C$28:$C$29))</f>
@@ -45478,35 +45496,35 @@
         <v>0.88632047658515611</v>
       </c>
       <c r="I62" s="41" t="s">
-        <v>3001</v>
+        <v>3000</v>
       </c>
       <c r="J62" s="42" t="s">
         <v>2671</v>
       </c>
       <c r="K62" s="67" t="s">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="L62" s="67">
         <v>174.16</v>
       </c>
       <c r="M62" s="68" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="N62" s="62">
         <f>M62*'Split Polyamides &amp; Isocyanates'!$C$37/L62</f>
         <v>0.6206878732200275</v>
       </c>
       <c r="O62" s="69" t="s">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="P62" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="Q62" s="51">
         <v>0.88</v>
       </c>
       <c r="R62" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="S62" s="54" cm="1">
         <f t="array" ref="S62">1-SUM(IF(ISNUMBER(P62:Q62), P62:Q62, 0))</f>
@@ -45515,13 +45533,13 @@
       <c r="T62" s="52"/>
       <c r="U62" s="56"/>
       <c r="V62" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="W62" s="51">
         <v>0.88</v>
       </c>
       <c r="X62" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="Y62" s="54" cm="1">
         <f t="array" ref="Y62">1-SUM(IF(ISNUMBER(V62:W62), V62:W62, 0))</f>
@@ -45542,13 +45560,13 @@
         <v>345</v>
       </c>
       <c r="C63" s="57" t="s">
-        <v>2818</v>
+        <v>2817</v>
       </c>
       <c r="D63" s="45" t="s">
+        <v>3003</v>
+      </c>
+      <c r="E63" s="41" t="s">
         <v>3004</v>
-      </c>
-      <c r="E63" s="41" t="s">
-        <v>3005</v>
       </c>
       <c r="F63" s="49">
         <f>'Split Polyamides &amp; Isocyanates'!C32*('Split Polyamides &amp; Isocyanates'!C28/SUM('Split Polyamides &amp; Isocyanates'!$C$28:$C$29))</f>
@@ -45563,35 +45581,35 @@
         <v>0.88632047658515611</v>
       </c>
       <c r="I63" s="41" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="J63" s="42" t="s">
         <v>2671</v>
       </c>
       <c r="K63" s="67" t="s">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="L63" s="67">
         <v>250.25</v>
       </c>
       <c r="M63" s="68" t="s">
-        <v>2948</v>
+        <v>2947</v>
       </c>
       <c r="N63" s="62">
         <f>M63*'Split Polyamides &amp; Isocyanates'!$C$37/L63</f>
         <v>0.71994005994005994</v>
       </c>
       <c r="O63" s="69" t="s">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="P63" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="Q63" s="51">
         <v>0.88</v>
       </c>
       <c r="R63" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="S63" s="54" cm="1">
         <f t="array" ref="S63">1-SUM(IF(ISNUMBER(P63:Q63), P63:Q63, 0))</f>
@@ -45600,13 +45618,13 @@
       <c r="T63" s="52"/>
       <c r="U63" s="56"/>
       <c r="V63" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="W63" s="51">
         <v>0.88</v>
       </c>
       <c r="X63" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="Y63" s="54" cm="1">
         <f t="array" ref="Y63">1-SUM(IF(ISNUMBER(V63:W63), V63:W63, 0))</f>
@@ -45627,13 +45645,13 @@
         <v>634</v>
       </c>
       <c r="C64" s="57" t="s">
-        <v>2808</v>
+        <v>2807</v>
       </c>
       <c r="D64" s="45" t="s">
+        <v>3008</v>
+      </c>
+      <c r="E64" s="41" t="s">
         <v>3009</v>
-      </c>
-      <c r="E64" s="41" t="s">
-        <v>3010</v>
       </c>
       <c r="F64" s="49">
         <f>'Split Polyamides &amp; Isocyanates'!C6*('Split Polyamides &amp; Isocyanates'!C24/('Split Polyamides &amp; Isocyanates'!C15+'Split Polyamides &amp; Isocyanates'!C24))</f>
@@ -45648,35 +45666,35 @@
         <v>0.87748442629671652</v>
       </c>
       <c r="I64" s="41" t="s">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="J64" s="42" t="s">
         <v>2661</v>
       </c>
       <c r="K64" s="67" t="s">
-        <v>3012</v>
+        <v>3011</v>
       </c>
       <c r="L64" s="67">
         <v>224.3</v>
       </c>
       <c r="M64" s="68" t="s">
-        <v>2908</v>
+        <v>2907</v>
       </c>
       <c r="N64" s="62">
         <f>M64*'Split Polyamides &amp; Isocyanates'!$C$37/L64</f>
         <v>0.64258582255907271</v>
       </c>
       <c r="O64" s="69" t="s">
-        <v>3013</v>
+        <v>3012</v>
       </c>
       <c r="P64" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="Q64" s="51">
         <v>0.91</v>
       </c>
       <c r="R64" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="S64" s="54" cm="1">
         <f t="array" ref="S64">1-SUM(IF(ISNUMBER(P64:Q64), P64:Q64, 0))</f>
@@ -45685,13 +45703,13 @@
       <c r="T64" s="52"/>
       <c r="U64" s="56"/>
       <c r="V64" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="W64" s="51">
         <v>0.91</v>
       </c>
       <c r="X64" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="Y64" s="54" cm="1">
         <f t="array" ref="Y64">1-SUM(IF(ISNUMBER(V64:W64), V64:W64, 0))</f>
@@ -45712,13 +45730,13 @@
         <v>634</v>
       </c>
       <c r="C65" s="57" t="s">
-        <v>2808</v>
+        <v>2807</v>
       </c>
       <c r="D65" s="45" t="s">
+        <v>3013</v>
+      </c>
+      <c r="E65" s="41" t="s">
         <v>3014</v>
-      </c>
-      <c r="E65" s="41" t="s">
-        <v>3015</v>
       </c>
       <c r="F65" s="49">
         <f>'Split Polyamides &amp; Isocyanates'!C6*('Split Polyamides &amp; Isocyanates'!C15/('Split Polyamides &amp; Isocyanates'!C15+'Split Polyamides &amp; Isocyanates'!C24))</f>
@@ -45733,35 +45751,35 @@
         <v>0.87748442629671652</v>
       </c>
       <c r="I65" s="41" t="s">
-        <v>3016</v>
+        <v>3015</v>
       </c>
       <c r="J65" s="42" t="s">
         <v>2661</v>
       </c>
       <c r="K65" s="67" t="s">
-        <v>3017</v>
+        <v>3016</v>
       </c>
       <c r="L65" s="67">
         <v>582.79999999999995</v>
       </c>
       <c r="M65" s="68" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="N65" s="62">
         <f>M65*'Split Polyamides &amp; Isocyanates'!$C$37/L65</f>
         <v>0.61827385037748805</v>
       </c>
       <c r="O65" s="69" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="P65" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="Q65" s="51">
         <v>0.91</v>
       </c>
       <c r="R65" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="S65" s="54" cm="1">
         <f t="array" ref="S65">1-SUM(IF(ISNUMBER(P65:Q65), P65:Q65, 0))</f>
@@ -45770,13 +45788,13 @@
       <c r="T65" s="52"/>
       <c r="U65" s="56"/>
       <c r="V65" s="52" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="W65" s="51">
         <v>0.91</v>
       </c>
       <c r="X65" s="52" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="Y65" s="54" cm="1">
         <f t="array" ref="Y65">1-SUM(IF(ISNUMBER(V65:W65), V65:W65, 0))</f>
@@ -45821,18 +45839,18 @@
   <sheetData>
     <row r="1" spans="1:9" ht="24" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="11" t="s">
-        <v>3047</v>
-      </c>
-      <c r="B1" s="95" t="s">
-        <v>3095</v>
+        <v>3046</v>
+      </c>
+      <c r="B1" s="94" t="s">
+        <v>3129</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="11" t="s">
-        <v>3049</v>
+        <v>3048</v>
       </c>
       <c r="B2" s="43" t="s">
-        <v>3096</v>
+        <v>3128</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
@@ -45850,10 +45868,10 @@
         <v>705</v>
       </c>
       <c r="E4" s="86" t="s">
-        <v>3092</v>
+        <v>3086</v>
       </c>
       <c r="F4" s="86" t="s">
-        <v>3093</v>
+        <v>3087</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -45881,7 +45899,7 @@
       </c>
       <c r="G5"/>
       <c r="H5" s="43" t="s">
-        <v>3094</v>
+        <v>3088</v>
       </c>
       <c r="I5" s="91">
         <f ca="1">PEARSON(E5:E147, F5:F147)</f>
@@ -49298,7 +49316,7 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B149" s="36" t="s">
-        <v>3088</v>
+        <v>3082</v>
       </c>
       <c r="C149" s="90">
         <f ca="1">SUM(C5:C147)</f>
@@ -49382,163 +49400,163 @@
   <sheetData>
     <row r="1" spans="1:3" ht="24" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="11" t="s">
+        <v>3046</v>
+      </c>
+      <c r="B1" s="94" t="s">
         <v>3047</v>
-      </c>
-      <c r="B1" s="95" t="s">
-        <v>3048</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="31" t="s">
+        <v>2758</v>
+      </c>
+      <c r="C3" s="32" t="s">
         <v>2759</v>
-      </c>
-      <c r="C3" s="32" t="s">
-        <v>2760</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B4" s="71" t="s">
+        <v>2760</v>
+      </c>
+      <c r="C4" s="33" t="s">
         <v>2761</v>
-      </c>
-      <c r="C4" s="33" t="s">
-        <v>2762</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B5" s="71" t="s">
+        <v>2762</v>
+      </c>
+      <c r="C5" s="33" t="s">
         <v>2763</v>
-      </c>
-      <c r="C5" s="33" t="s">
-        <v>2764</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B6" s="71" t="s">
+        <v>2764</v>
+      </c>
+      <c r="C6" s="33" t="s">
         <v>2765</v>
-      </c>
-      <c r="C6" s="33" t="s">
-        <v>2766</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B7" s="71" t="s">
+        <v>2766</v>
+      </c>
+      <c r="C7" s="33" t="s">
         <v>2767</v>
-      </c>
-      <c r="C7" s="33" t="s">
-        <v>2768</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B8" s="71" t="s">
+        <v>2768</v>
+      </c>
+      <c r="C8" s="33" t="s">
         <v>2769</v>
-      </c>
-      <c r="C8" s="33" t="s">
-        <v>2770</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B9" s="71" t="s">
+        <v>2770</v>
+      </c>
+      <c r="C9" s="33" t="s">
         <v>2771</v>
-      </c>
-      <c r="C9" s="33" t="s">
-        <v>2772</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B10" s="71" t="s">
+        <v>2772</v>
+      </c>
+      <c r="C10" s="33" t="s">
         <v>2773</v>
-      </c>
-      <c r="C10" s="33" t="s">
-        <v>2774</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B11" s="71" t="s">
+        <v>2774</v>
+      </c>
+      <c r="C11" s="33" t="s">
         <v>2775</v>
-      </c>
-      <c r="C11" s="33" t="s">
-        <v>2776</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B12" s="71" t="s">
+        <v>2776</v>
+      </c>
+      <c r="C12" s="33" t="s">
         <v>2777</v>
-      </c>
-      <c r="C12" s="33" t="s">
-        <v>2778</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B13" s="71" t="s">
+        <v>2778</v>
+      </c>
+      <c r="C13" s="33" t="s">
         <v>2779</v>
-      </c>
-      <c r="C13" s="33" t="s">
-        <v>2780</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B14" s="71" t="s">
+        <v>2780</v>
+      </c>
+      <c r="C14" s="33" t="s">
         <v>2781</v>
-      </c>
-      <c r="C14" s="33" t="s">
-        <v>2782</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B15" s="71" t="s">
+        <v>2782</v>
+      </c>
+      <c r="C15" s="33" t="s">
         <v>2783</v>
-      </c>
-      <c r="C15" s="33" t="s">
-        <v>2784</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B16" s="71" t="s">
+        <v>2784</v>
+      </c>
+      <c r="C16" s="33" t="s">
         <v>2785</v>
-      </c>
-      <c r="C16" s="33" t="s">
-        <v>2786</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B17" s="71" t="s">
+        <v>2786</v>
+      </c>
+      <c r="C17" s="33" t="s">
         <v>2787</v>
-      </c>
-      <c r="C17" s="33" t="s">
-        <v>2788</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B18" s="71" t="s">
+        <v>2788</v>
+      </c>
+      <c r="C18" s="33" t="s">
         <v>2789</v>
-      </c>
-      <c r="C18" s="33" t="s">
-        <v>2790</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B19" s="71" t="s">
+        <v>2790</v>
+      </c>
+      <c r="C19" s="33" t="s">
         <v>2791</v>
-      </c>
-      <c r="C19" s="33" t="s">
-        <v>2792</v>
       </c>
     </row>
     <row r="20" spans="2:3" s="43" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B20" s="71" t="s">
-        <v>3135</v>
+        <v>3125</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>3134</v>
+        <v>3124</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="72" t="s">
+        <v>2792</v>
+      </c>
+      <c r="C21" s="34" t="s">
         <v>2793</v>
-      </c>
-      <c r="C21" s="34" t="s">
-        <v>2794</v>
       </c>
     </row>
   </sheetData>

--- a/Article_data/Step 3 - PRODCOM results.xlsx
+++ b/Article_data/Step 3 - PRODCOM results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\nicolas\projects\202604-paper-1-supplementary-code\Article_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A1107EF-031A-4030-A1C2-AD29DCE61D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9A410E9-0DCB-4E3B-B130-41E11FF91EF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15720" tabRatio="570" xr2:uid="{EE4678C9-3BCB-4D41-A2DA-6855614353C7}"/>
   </bookViews>
